--- a/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_01.xlsx
+++ b/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_01.xlsx
@@ -603,7 +603,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
         <v>13</v>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="AA2" t="n">
         <v>0.7</v>
@@ -659,7 +659,7 @@
         <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.7484999999999999</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="3">
@@ -697,7 +697,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K3" t="n">
         <v>13</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1</v>
@@ -753,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8320000000000001</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="4">
@@ -791,7 +791,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
         <v>13</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="AA4" t="n">
         <v>0.7</v>
@@ -847,7 +847,7 @@
         <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="5">
@@ -1167,10 +1167,10 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>35</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="AA8" t="n">
         <v>0.93</v>
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.6465000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1261,10 +1261,10 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>35</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="AA9" t="n">
         <v>0.7</v>
@@ -1317,7 +1317,7 @@
         <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6459999999999999</v>
+        <v>0.6199999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1355,10 +1355,10 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
         <v>35</v>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="AA10" t="n">
         <v>0.41</v>
@@ -1411,7 +1411,7 @@
         <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.6034999999999999</v>
+        <v>0.5740000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1449,13 +1449,13 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
         <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1490,22 +1490,22 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AA11" t="n">
         <v>0.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.7885000000000001</v>
+        <v>0.6964999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1543,13 +1543,13 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
         <v>13</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="AA12" t="n">
         <v>0.86</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="AC12" t="n">
         <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.7204999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1637,13 +1637,13 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
         <v>13</v>
       </c>
       <c r="L13" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1678,22 +1678,22 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="AA13" t="n">
         <v>0.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="AC13" t="n">
         <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.8135</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="14">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="AA14" t="n">
         <v>0.86</v>
@@ -1787,7 +1787,7 @@
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.8470000000000001</v>
+        <v>0.8340000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="AA15" t="n">
         <v>0.93</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.875</v>
+        <v>0.8620000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="AA16" t="n">
         <v>0.7</v>
@@ -1975,7 +1975,7 @@
         <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.839</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         <v>13</v>
       </c>
       <c r="L23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2627,13 +2627,13 @@
         <v>1</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AC23" t="n">
         <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7444999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2677,7 +2677,7 @@
         <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2721,13 +2721,13 @@
         <v>0.78</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.726</v>
+        <v>0.7230000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -2771,7 +2771,7 @@
         <v>13</v>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2815,13 +2815,13 @@
         <v>0.51</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AC25" t="n">
         <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.6975</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -2859,13 +2859,13 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K26" t="n">
         <v>13</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AA26" t="n">
         <v>0.78</v>
@@ -2915,7 +2915,7 @@
         <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.8595</v>
+        <v>0.8530000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2953,13 +2953,13 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K27" t="n">
         <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
@@ -3009,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.8905000000000001</v>
+        <v>0.8839999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3047,13 +3047,13 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
         <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AA28" t="n">
         <v>0.78</v>
@@ -3103,7 +3103,7 @@
         <v>3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.83</v>
+        <v>0.8205</v>
       </c>
     </row>
     <row r="29">
@@ -3708,7 +3708,7 @@
         <v>13</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L35" t="n">
         <v>3</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="Z35" t="n">
         <v>0.97</v>
@@ -3761,7 +3761,7 @@
         <v>3</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.883</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="36">
@@ -3802,7 +3802,7 @@
         <v>13</v>
       </c>
       <c r="K36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L36" t="n">
         <v>3</v>
@@ -3843,7 +3843,7 @@
         <v>0.96</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AA36" t="n">
         <v>0.93</v>
@@ -3855,7 +3855,7 @@
         <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.9195</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="37">
@@ -3896,7 +3896,7 @@
         <v>13</v>
       </c>
       <c r="K37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AA37" t="n">
         <v>0.86</v>
@@ -3949,7 +3949,7 @@
         <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.8955</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="38">
@@ -3990,7 +3990,7 @@
         <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L38" t="n">
         <v>3</v>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AA38" t="n">
         <v>1</v>
@@ -4043,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.8494999999999999</v>
+        <v>0.8399999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -4084,7 +4084,7 @@
         <v>13</v>
       </c>
       <c r="K39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L39" t="n">
         <v>3</v>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AA39" t="n">
         <v>0.73</v>
@@ -4137,7 +4137,7 @@
         <v>2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.8055000000000001</v>
+        <v>0.7955000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -4178,7 +4178,7 @@
         <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AA40" t="n">
         <v>0.38</v>
@@ -4231,7 +4231,7 @@
         <v>3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.7449999999999999</v>
+        <v>0.7355</v>
       </c>
     </row>
     <row r="41">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AA47" t="n">
         <v>0.61</v>
@@ -4889,7 +4889,7 @@
         <v>3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.719</v>
+        <v>0.7254999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Y48" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.72</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.71</v>
       </c>
       <c r="AA48" t="n">
         <v>0.86</v>
@@ -4983,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.746</v>
+        <v>0.7525000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA49" t="n">
         <v>0.93</v>
@@ -5077,7 +5077,7 @@
         <v>2</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.7375</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="50">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="AA50" t="n">
         <v>0.93</v>
@@ -5171,7 +5171,7 @@
         <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.7355</v>
+        <v>0.7869999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="AA51" t="n">
         <v>0.86</v>
@@ -5265,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="52">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="AA52" t="n">
         <v>0.61</v>
@@ -5359,7 +5359,7 @@
         <v>3</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.72</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="53">
@@ -5961,13 +5961,13 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
+        <v>13</v>
+      </c>
+      <c r="K59" t="n">
         <v>14</v>
       </c>
-      <c r="K59" t="n">
-        <v>13</v>
-      </c>
       <c r="L59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -6002,22 +6002,22 @@
         </is>
       </c>
       <c r="Y59" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="AA59" t="n">
         <v>0.63</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AC59" t="n">
         <v>2</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.62</v>
+        <v>0.6114999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -6055,13 +6055,13 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
+        <v>13</v>
+      </c>
+      <c r="K60" t="n">
         <v>14</v>
       </c>
-      <c r="K60" t="n">
-        <v>13</v>
-      </c>
       <c r="L60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -6096,22 +6096,22 @@
         </is>
       </c>
       <c r="Y60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="AA60" t="n">
         <v>0.92</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AC60" t="n">
         <v>1</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.6455000000000001</v>
+        <v>0.6405000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -6149,13 +6149,13 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
+        <v>13</v>
+      </c>
+      <c r="K61" t="n">
         <v>14</v>
       </c>
-      <c r="K61" t="n">
-        <v>13</v>
-      </c>
       <c r="L61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -6190,22 +6190,22 @@
         </is>
       </c>
       <c r="Y61" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AA61" t="n">
         <v>0.83</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AC61" t="n">
         <v>3</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.5980000000000001</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="62">
@@ -6525,7 +6525,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
         <v>13</v>
@@ -6566,10 +6566,10 @@
         </is>
       </c>
       <c r="Y65" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="AA65" t="n">
         <v>0.92</v>
@@ -6581,7 +6581,7 @@
         <v>2</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.5965</v>
+        <v>0.6095</v>
       </c>
     </row>
     <row r="66">
@@ -6619,7 +6619,7 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K66" t="n">
         <v>13</v>
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="Y66" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AA66" t="n">
         <v>0.83</v>
@@ -6675,7 +6675,7 @@
         <v>1</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.6154999999999999</v>
+        <v>0.6220000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -6713,7 +6713,7 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
         <v>13</v>
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Y67" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="AA67" t="n">
         <v>0.51</v>
@@ -6769,7 +6769,7 @@
         <v>3</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.5805</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="68">
@@ -6807,7 +6807,7 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K68" t="n">
         <v>13</v>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Y68" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="AA68" t="n">
         <v>0.59</v>
@@ -6863,7 +6863,7 @@
         <v>2</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.604</v>
+        <v>0.7274999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -6901,7 +6901,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K69" t="n">
         <v>13</v>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Y69" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="Z69" t="n">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="AA69" t="n">
         <v>0.91</v>
@@ -6957,7 +6957,7 @@
         <v>1</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.6355000000000001</v>
+        <v>0.7689999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -6995,7 +6995,7 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K70" t="n">
         <v>13</v>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Y70" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="Z70" t="n">
-        <v>0.51</v>
+        <v>0.72</v>
       </c>
       <c r="AA70" t="n">
         <v>0.8100000000000001</v>
@@ -7051,7 +7051,7 @@
         <v>3</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.5865</v>
+        <v>0.726</v>
       </c>
     </row>
     <row r="71">
@@ -7371,7 +7371,7 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K74" t="n">
         <v>10</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Y74" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z74" t="n">
         <v>0.14</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0.16</v>
       </c>
       <c r="AA74" t="n">
         <v>1</v>
@@ -7424,10 +7424,10 @@
         <v>0.79</v>
       </c>
       <c r="AC74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.4165</v>
+        <v>0.4005</v>
       </c>
     </row>
     <row r="75">
@@ -7465,7 +7465,7 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K75" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="Y75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Z75" t="n">
         <v>0.21</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0.23</v>
       </c>
       <c r="AA75" t="n">
         <v>0.78</v>
@@ -7521,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.418</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="76">
@@ -7559,7 +7559,7 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K76" t="n">
         <v>10</v>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Y76" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Z76" t="n">
         <v>0.28</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0.29</v>
       </c>
       <c r="AA76" t="n">
         <v>0.51</v>
@@ -7612,10 +7612,10 @@
         <v>0.82</v>
       </c>
       <c r="AC76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.4105</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="77">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7934,20 +7934,10 @@
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="n">
-        <v>13</v>
-      </c>
-      <c r="K80" t="n">
-        <v>13</v>
-      </c>
-      <c r="L80" t="n">
-        <v>20</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
@@ -7956,42 +7946,38 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="U80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V80" t="b">
         <v>0</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
+          <t>Alternative 1 (extraction failed)</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
       <c r="Y80" t="n">
-        <v>0.6899999999999999</v>
+        <v>1928</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.71</v>
+        <v>1928</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.7</v>
+        <v>1928</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.63</v>
+        <v>1928</v>
       </c>
       <c r="AC80" t="n">
-        <v>2</v>
+        <v>1928</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.6899999999999999</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="81">
@@ -8015,7 +8001,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -8028,20 +8014,10 @@
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="n">
-        <v>13</v>
-      </c>
-      <c r="K81" t="n">
-        <v>13</v>
-      </c>
-      <c r="L81" t="n">
-        <v>20</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
@@ -8050,42 +8026,38 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="U81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="b">
         <v>0</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
+          <t>Alternative 2 (extraction failed)</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr"/>
       <c r="Y81" t="n">
-        <v>0.65</v>
+        <v>1928</v>
       </c>
       <c r="Z81" t="n">
-        <v>0.67</v>
+        <v>1928</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.93</v>
+        <v>1928</v>
       </c>
       <c r="AB81" t="n">
-        <v>0.63</v>
+        <v>1928</v>
       </c>
       <c r="AC81" t="n">
-        <v>1</v>
+        <v>1928</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.7100000000000001</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="82">
@@ -8109,7 +8081,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8122,20 +8094,10 @@
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="n">
-        <v>13</v>
-      </c>
-      <c r="K82" t="n">
-        <v>13</v>
-      </c>
-      <c r="L82" t="n">
-        <v>20</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
@@ -8144,42 +8106,38 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="U82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" t="b">
         <v>0</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>Alternative 3 (extraction failed)</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr"/>
       <c r="Y82" t="n">
-        <v>0.61</v>
+        <v>1928</v>
       </c>
       <c r="Z82" t="n">
-        <v>0.64</v>
+        <v>1928</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.86</v>
+        <v>1928</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.63</v>
+        <v>1928</v>
       </c>
       <c r="AC82" t="n">
-        <v>3</v>
+        <v>1928</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.6735</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="83">
@@ -8217,7 +8175,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K83" t="n">
         <v>13</v>
@@ -8258,10 +8216,10 @@
         </is>
       </c>
       <c r="Y83" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="Z83" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AA83" t="n">
         <v>0.85</v>
@@ -8270,10 +8228,10 @@
         <v>0.68</v>
       </c>
       <c r="AC83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.4285</v>
+        <v>0.4835</v>
       </c>
     </row>
     <row r="84">
@@ -8311,7 +8269,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K84" t="n">
         <v>13</v>
@@ -8352,10 +8310,10 @@
         </is>
       </c>
       <c r="Y84" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="Z84" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="AA84" t="n">
         <v>0.67</v>
@@ -8364,10 +8322,10 @@
         <v>0.75</v>
       </c>
       <c r="AC84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.429</v>
+        <v>0.4775</v>
       </c>
     </row>
     <row r="85">
@@ -8405,7 +8363,7 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K85" t="n">
         <v>13</v>
@@ -8446,10 +8404,10 @@
         </is>
       </c>
       <c r="Y85" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="Z85" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="AA85" t="n">
         <v>0.45</v>
@@ -8461,7 +8419,7 @@
         <v>3</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.4075</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="86">
@@ -8499,13 +8457,13 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K86" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L86" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -8540,22 +8498,22 @@
         </is>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA86" t="n">
         <v>0.73</v>
       </c>
       <c r="AB86" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC86" t="n">
         <v>1</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.2585</v>
+        <v>0.3945</v>
       </c>
     </row>
     <row r="87">
@@ -8593,13 +8551,13 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L87" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -8634,22 +8592,22 @@
         </is>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AA87" t="n">
         <v>0.51</v>
       </c>
       <c r="AB87" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC87" t="n">
         <v>2</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.2145</v>
+        <v>0.3765</v>
       </c>
     </row>
     <row r="88">
@@ -8687,13 +8645,13 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L88" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -8728,22 +8686,22 @@
         </is>
       </c>
       <c r="Y88" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.03</v>
+        <v>0.28</v>
       </c>
       <c r="AA88" t="n">
         <v>0.23</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="AC88" t="n">
         <v>3</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.1585</v>
+        <v>0.3315</v>
       </c>
     </row>
     <row r="89">
@@ -8781,13 +8739,13 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K89" t="n">
         <v>13</v>
       </c>
       <c r="L89" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -8822,22 +8780,22 @@
         </is>
       </c>
       <c r="Y89" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Z89" t="n">
         <v>0.5</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0.51</v>
       </c>
       <c r="AA89" t="n">
         <v>0.93</v>
       </c>
       <c r="AB89" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AC89" t="n">
         <v>1</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.639</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="90">
@@ -8875,13 +8833,13 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K90" t="n">
         <v>13</v>
       </c>
       <c r="L90" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -8916,22 +8874,22 @@
         </is>
       </c>
       <c r="Y90" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Z90" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0.54</v>
       </c>
       <c r="AA90" t="n">
         <v>0.78</v>
       </c>
       <c r="AB90" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6205000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -8969,13 +8927,13 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K91" t="n">
         <v>13</v>
       </c>
       <c r="L91" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -9010,7 +8968,7 @@
         </is>
       </c>
       <c r="Y91" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="Z91" t="n">
         <v>0.5600000000000001</v>
@@ -9019,13 +8977,13 @@
         <v>0.61</v>
       </c>
       <c r="AB91" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AC91" t="n">
         <v>3</v>
       </c>
       <c r="AD91" t="n">
-        <v>0.6104999999999999</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="92">
@@ -9063,10 +9021,10 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L92" t="n">
         <v>8</v>
@@ -9104,10 +9062,10 @@
         </is>
       </c>
       <c r="Y92" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="AA92" t="n">
         <v>0.45</v>
@@ -9119,7 +9077,7 @@
         <v>2</v>
       </c>
       <c r="AD92" t="n">
-        <v>0.61</v>
+        <v>0.6295000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -9157,10 +9115,10 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L93" t="n">
         <v>8</v>
@@ -9198,10 +9156,10 @@
         </is>
       </c>
       <c r="Y93" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z93" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA93" t="n">
         <v>1</v>
@@ -9213,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="AD93" t="n">
-        <v>0.675</v>
+        <v>0.6945000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -9251,10 +9209,10 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L94" t="n">
         <v>8</v>
@@ -9292,10 +9250,10 @@
         </is>
       </c>
       <c r="Y94" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AA94" t="n">
         <v>0.45</v>
@@ -9307,7 +9265,7 @@
         <v>3</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.503</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="95">
@@ -9345,7 +9303,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K95" t="n">
         <v>13</v>
@@ -9386,10 +9344,10 @@
         </is>
       </c>
       <c r="Y95" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AA95" t="n">
         <v>0.86</v>
@@ -9401,7 +9359,7 @@
         <v>1</v>
       </c>
       <c r="AD95" t="n">
-        <v>0.4365</v>
+        <v>0.4525</v>
       </c>
     </row>
     <row r="96">
@@ -9439,7 +9397,7 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K96" t="n">
         <v>13</v>
@@ -9480,10 +9438,10 @@
         </is>
       </c>
       <c r="Y96" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="Z96" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="AA96" t="n">
         <v>0.7</v>
@@ -9495,7 +9453,7 @@
         <v>2</v>
       </c>
       <c r="AD96" t="n">
-        <v>0.4269999999999999</v>
+        <v>0.4435</v>
       </c>
     </row>
     <row r="97">
@@ -9533,7 +9491,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K97" t="n">
         <v>13</v>
@@ -9574,10 +9532,10 @@
         </is>
       </c>
       <c r="Y97" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="Z97" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="AA97" t="n">
         <v>0.51</v>
@@ -9589,7 +9547,7 @@
         <v>3</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.412</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="98">
@@ -9909,10 +9867,10 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K101" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L101" t="n">
         <v>35</v>
@@ -9950,10 +9908,10 @@
         </is>
       </c>
       <c r="Y101" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="Z101" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="AA101" t="n">
         <v>0.86</v>
@@ -9965,7 +9923,7 @@
         <v>1</v>
       </c>
       <c r="AD101" t="n">
-        <v>0.6160000000000001</v>
+        <v>0.6615</v>
       </c>
     </row>
     <row r="102">
@@ -10003,10 +9961,10 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K102" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L102" t="n">
         <v>35</v>
@@ -10044,10 +10002,10 @@
         </is>
       </c>
       <c r="Y102" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="Z102" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="AA102" t="n">
         <v>0.7</v>
@@ -10059,7 +10017,7 @@
         <v>2</v>
       </c>
       <c r="AD102" t="n">
-        <v>0.608</v>
+        <v>0.6535</v>
       </c>
     </row>
     <row r="103">
@@ -10097,10 +10055,10 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K103" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L103" t="n">
         <v>35</v>
@@ -10138,10 +10096,10 @@
         </is>
       </c>
       <c r="Y103" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="Z103" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="AA103" t="n">
         <v>0.51</v>
@@ -10153,7 +10111,7 @@
         <v>3</v>
       </c>
       <c r="AD103" t="n">
-        <v>0.583</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="104">
@@ -10479,7 +10437,7 @@
         <v>13</v>
       </c>
       <c r="L107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -10523,13 +10481,13 @@
         <v>0.78</v>
       </c>
       <c r="AB107" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AC107" t="n">
         <v>3</v>
       </c>
       <c r="AD107" t="n">
-        <v>0.6815</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -10573,7 +10531,7 @@
         <v>13</v>
       </c>
       <c r="L108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -10617,13 +10575,13 @@
         <v>1</v>
       </c>
       <c r="AB108" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AC108" t="n">
         <v>2</v>
       </c>
       <c r="AD108" t="n">
-        <v>0.758</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="109">
@@ -10667,7 +10625,7 @@
         <v>13</v>
       </c>
       <c r="L109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -11037,7 +10995,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K113" t="n">
         <v>13</v>
@@ -11131,7 +11089,7 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K114" t="n">
         <v>13</v>
@@ -11225,7 +11183,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K115" t="n">
         <v>13</v>
@@ -11322,7 +11280,7 @@
         <v>13</v>
       </c>
       <c r="K116" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L116" t="n">
         <v>25</v>
@@ -11360,10 +11318,10 @@
         </is>
       </c>
       <c r="Y116" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="Z116" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AA116" t="n">
         <v>0.61</v>
@@ -11375,7 +11333,7 @@
         <v>2</v>
       </c>
       <c r="AD116" t="n">
-        <v>0.8345</v>
+        <v>0.8115</v>
       </c>
     </row>
     <row r="117">
@@ -11416,7 +11374,7 @@
         <v>13</v>
       </c>
       <c r="K117" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L117" t="n">
         <v>25</v>
@@ -11454,10 +11412,10 @@
         </is>
       </c>
       <c r="Y117" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="Z117" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AA117" t="n">
         <v>0.86</v>
@@ -11469,7 +11427,7 @@
         <v>1</v>
       </c>
       <c r="AD117" t="n">
-        <v>0.8520000000000001</v>
+        <v>0.8195</v>
       </c>
     </row>
     <row r="118">
@@ -11510,7 +11468,7 @@
         <v>13</v>
       </c>
       <c r="K118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L118" t="n">
         <v>25</v>
@@ -11548,10 +11506,10 @@
         </is>
       </c>
       <c r="Y118" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="Z118" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="AA118" t="n">
         <v>0.86</v>
@@ -11563,7 +11521,7 @@
         <v>3</v>
       </c>
       <c r="AD118" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7709999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -11607,7 +11565,7 @@
         <v>13</v>
       </c>
       <c r="L119" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -11651,13 +11609,13 @@
         <v>0.67</v>
       </c>
       <c r="AB119" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="AC119" t="n">
         <v>2</v>
       </c>
       <c r="AD119" t="n">
-        <v>0.8865000000000001</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="120">
@@ -11701,7 +11659,7 @@
         <v>13</v>
       </c>
       <c r="L120" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -11745,13 +11703,13 @@
         <v>1</v>
       </c>
       <c r="AB120" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="AC120" t="n">
         <v>1</v>
       </c>
       <c r="AD120" t="n">
-        <v>0.9164999999999999</v>
+        <v>0.9089999999999999</v>
       </c>
     </row>
     <row r="121">
@@ -11795,7 +11753,7 @@
         <v>13</v>
       </c>
       <c r="L121" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -11839,13 +11797,13 @@
         <v>0.67</v>
       </c>
       <c r="AB121" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="AC121" t="n">
         <v>3</v>
       </c>
       <c r="AD121" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="122">
@@ -12450,14 +12408,14 @@
         <v>14</v>
       </c>
       <c r="K128" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L128" t="n">
         <v>25</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -12488,10 +12446,10 @@
         </is>
       </c>
       <c r="Y128" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="Z128" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="AA128" t="n">
         <v>0.86</v>
@@ -12500,10 +12458,10 @@
         <v>0.79</v>
       </c>
       <c r="AC128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD128" t="n">
-        <v>0.6575</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -12544,14 +12502,14 @@
         <v>14</v>
       </c>
       <c r="K129" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L129" t="n">
         <v>25</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -12582,10 +12540,10 @@
         </is>
       </c>
       <c r="Y129" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="Z129" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA129" t="n">
         <v>0.15</v>
@@ -12597,7 +12555,7 @@
         <v>3</v>
       </c>
       <c r="AD129" t="n">
-        <v>0.5325</v>
+        <v>0.5549999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -12638,14 +12596,14 @@
         <v>14</v>
       </c>
       <c r="K130" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L130" t="n">
         <v>25</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -12688,7 +12646,7 @@
         <v>0.15</v>
       </c>
       <c r="AC130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD130" t="n">
         <v>0.6724999999999999</v>
@@ -12729,17 +12687,17 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K131" t="n">
         <v>13</v>
       </c>
       <c r="L131" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -12770,10 +12728,10 @@
         </is>
       </c>
       <c r="Y131" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="Z131" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AA131" t="n">
         <v>0.86</v>
@@ -12785,7 +12743,7 @@
         <v>1</v>
       </c>
       <c r="AD131" t="n">
-        <v>0.7755000000000001</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="132">
@@ -12823,17 +12781,17 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K132" t="n">
         <v>13</v>
       </c>
       <c r="L132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -12864,10 +12822,10 @@
         </is>
       </c>
       <c r="Y132" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z132" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA132" t="n">
         <v>0.15</v>
@@ -12879,7 +12837,7 @@
         <v>3</v>
       </c>
       <c r="AD132" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="133">
@@ -12917,17 +12875,17 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K133" t="n">
         <v>13</v>
       </c>
       <c r="L133" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -13011,7 +12969,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K134" t="n">
         <v>13</v>
@@ -13052,10 +13010,10 @@
         </is>
       </c>
       <c r="Y134" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="Z134" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AA134" t="n">
         <v>0.76</v>
@@ -13067,7 +13025,7 @@
         <v>3</v>
       </c>
       <c r="AD134" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6440000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -13105,7 +13063,7 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K135" t="n">
         <v>13</v>
@@ -13146,10 +13104,10 @@
         </is>
       </c>
       <c r="Y135" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="Z135" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="AA135" t="n">
         <v>0.93</v>
@@ -13161,7 +13119,7 @@
         <v>1</v>
       </c>
       <c r="AD135" t="n">
-        <v>0.6970000000000001</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="136">
@@ -13199,7 +13157,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K136" t="n">
         <v>13</v>
@@ -13240,10 +13198,10 @@
         </is>
       </c>
       <c r="Y136" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="Z136" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="AA136" t="n">
         <v>0.67</v>
@@ -13255,7 +13213,7 @@
         <v>2</v>
       </c>
       <c r="AD136" t="n">
-        <v>0.671</v>
+        <v>0.6775</v>
       </c>
     </row>
     <row r="137">
@@ -13575,10 +13533,10 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K140" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L140" t="n">
         <v>25</v>
@@ -13616,10 +13574,10 @@
         </is>
       </c>
       <c r="Y140" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z140" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="AA140" t="n">
         <v>0.7</v>
@@ -13631,7 +13589,7 @@
         <v>2</v>
       </c>
       <c r="AD140" t="n">
-        <v>0.781</v>
+        <v>0.6869999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -13669,10 +13627,10 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K141" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L141" t="n">
         <v>25</v>
@@ -13710,10 +13668,10 @@
         </is>
       </c>
       <c r="Y141" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="Z141" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="AA141" t="n">
         <v>1</v>
@@ -13725,7 +13683,7 @@
         <v>1</v>
       </c>
       <c r="AD141" t="n">
-        <v>0.8150000000000001</v>
+        <v>0.7115</v>
       </c>
     </row>
     <row r="142">
@@ -13763,10 +13721,10 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K142" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L142" t="n">
         <v>25</v>
@@ -13804,10 +13762,10 @@
         </is>
       </c>
       <c r="Y142" t="n">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="Z142" t="n">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="AA142" t="n">
         <v>0.78</v>
@@ -13819,7 +13777,7 @@
         <v>3</v>
       </c>
       <c r="AD142" t="n">
-        <v>0.755</v>
+        <v>0.6415000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -13857,10 +13815,10 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L143" t="n">
         <v>3</v>
@@ -13898,10 +13856,10 @@
         </is>
       </c>
       <c r="Y143" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="Z143" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AA143" t="n">
         <v>0.78</v>
@@ -13913,7 +13871,7 @@
         <v>2</v>
       </c>
       <c r="AD143" t="n">
-        <v>0.792</v>
+        <v>0.7205</v>
       </c>
     </row>
     <row r="144">
@@ -13951,10 +13909,10 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L144" t="n">
         <v>3</v>
@@ -13992,10 +13950,10 @@
         </is>
       </c>
       <c r="Y144" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="Z144" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="AA144" t="n">
         <v>1</v>
@@ -14007,7 +13965,7 @@
         <v>1</v>
       </c>
       <c r="AD144" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.7385</v>
       </c>
     </row>
     <row r="145">
@@ -14045,10 +14003,10 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K145" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
@@ -14086,10 +14044,10 @@
         </is>
       </c>
       <c r="Y145" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="Z145" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="AA145" t="n">
         <v>0.61</v>
@@ -14101,7 +14059,7 @@
         <v>3</v>
       </c>
       <c r="AD145" t="n">
-        <v>0.6995</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="146">
@@ -14139,7 +14097,7 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K146" t="n">
         <v>14</v>
@@ -14180,10 +14138,10 @@
         </is>
       </c>
       <c r="Y146" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="Z146" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AA146" t="n">
         <v>0.7</v>
@@ -14192,10 +14150,10 @@
         <v>0.73</v>
       </c>
       <c r="AC146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD146" t="n">
-        <v>0.8510000000000001</v>
+        <v>0.8995</v>
       </c>
     </row>
     <row r="147">
@@ -14233,7 +14191,7 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K147" t="n">
         <v>14</v>
@@ -14274,10 +14232,10 @@
         </is>
       </c>
       <c r="Y147" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="Z147" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA147" t="n">
         <v>0.93</v>
@@ -14289,7 +14247,7 @@
         <v>1</v>
       </c>
       <c r="AD147" t="n">
-        <v>0.8775000000000002</v>
+        <v>0.9455</v>
       </c>
     </row>
     <row r="148">
@@ -14327,7 +14285,7 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K148" t="n">
         <v>14</v>
@@ -14368,10 +14326,10 @@
         </is>
       </c>
       <c r="Y148" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="Z148" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="AA148" t="n">
         <v>0.78</v>
@@ -14380,10 +14338,10 @@
         <v>0.73</v>
       </c>
       <c r="AC148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD148" t="n">
-        <v>0.8280000000000001</v>
+        <v>0.9025000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -14427,7 +14385,7 @@
         <v>13</v>
       </c>
       <c r="L149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -14471,13 +14429,13 @@
         <v>0.45</v>
       </c>
       <c r="AB149" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="AC149" t="n">
         <v>3</v>
       </c>
       <c r="AD149" t="n">
-        <v>0.348</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="150">
@@ -14521,7 +14479,7 @@
         <v>13</v>
       </c>
       <c r="L150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
@@ -14565,13 +14523,13 @@
         <v>0.93</v>
       </c>
       <c r="AB150" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AC150" t="n">
         <v>2</v>
       </c>
       <c r="AD150" t="n">
-        <v>0.5185</v>
+        <v>0.5095000000000001</v>
       </c>
     </row>
     <row r="151">
@@ -14615,7 +14573,7 @@
         <v>13</v>
       </c>
       <c r="L151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -14659,13 +14617,13 @@
         <v>0.67</v>
       </c>
       <c r="AB151" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AC151" t="n">
         <v>1</v>
       </c>
       <c r="AD151" t="n">
-        <v>0.522</v>
+        <v>0.5129999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -14988,7 +14946,7 @@
         <v>13</v>
       </c>
       <c r="K155" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L155" t="n">
         <v>13</v>
@@ -15082,7 +15040,7 @@
         <v>13</v>
       </c>
       <c r="K156" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L156" t="n">
         <v>13</v>
@@ -15176,7 +15134,7 @@
         <v>13</v>
       </c>
       <c r="K157" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L157" t="n">
         <v>13</v>
@@ -15549,7 +15507,7 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K161" t="n">
         <v>13</v>
@@ -15643,7 +15601,7 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K162" t="n">
         <v>13</v>
@@ -15696,7 +15654,7 @@
         <v>0.72</v>
       </c>
       <c r="AC162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD162" t="n">
         <v>0.9279999999999999</v>
@@ -15737,7 +15695,7 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K163" t="n">
         <v>13</v>
@@ -15778,10 +15736,10 @@
         </is>
       </c>
       <c r="Y163" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="Z163" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="AA163" t="n">
         <v>0.93</v>
@@ -15790,10 +15748,10 @@
         <v>0.72</v>
       </c>
       <c r="AC163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD163" t="n">
-        <v>0.9275</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="164">
@@ -15831,7 +15789,7 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K164" t="n">
         <v>13</v>
@@ -15925,7 +15883,7 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K165" t="n">
         <v>13</v>
@@ -16019,7 +15977,7 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K166" t="n">
         <v>13</v>
@@ -16116,7 +16074,7 @@
         <v>20</v>
       </c>
       <c r="K167" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L167" t="n">
         <v>18</v>
@@ -16154,10 +16112,10 @@
         </is>
       </c>
       <c r="Y167" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="Z167" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="AA167" t="n">
         <v>0.7</v>
@@ -16169,7 +16127,7 @@
         <v>3</v>
       </c>
       <c r="AD167" t="n">
-        <v>0.833</v>
+        <v>0.8200000000000001</v>
       </c>
     </row>
     <row r="168">
@@ -16210,7 +16168,7 @@
         <v>20</v>
       </c>
       <c r="K168" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L168" t="n">
         <v>18</v>
@@ -16248,10 +16206,10 @@
         </is>
       </c>
       <c r="Y168" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="Z168" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="AA168" t="n">
         <v>1</v>
@@ -16263,7 +16221,7 @@
         <v>2</v>
       </c>
       <c r="AD168" t="n">
-        <v>0.9059999999999999</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="169">
@@ -16304,7 +16262,7 @@
         <v>20</v>
       </c>
       <c r="K169" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L169" t="n">
         <v>18</v>
@@ -16395,7 +16353,7 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K170" t="n">
         <v>13</v>
@@ -16436,10 +16394,10 @@
         </is>
       </c>
       <c r="Y170" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="Z170" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="AA170" t="n">
         <v>0.67</v>
@@ -16451,7 +16409,7 @@
         <v>3</v>
       </c>
       <c r="AD170" t="n">
-        <v>0.5565</v>
+        <v>0.5825</v>
       </c>
     </row>
     <row r="171">
@@ -16489,7 +16447,7 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K171" t="n">
         <v>13</v>
@@ -16530,10 +16488,10 @@
         </is>
       </c>
       <c r="Y171" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="Z171" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="AA171" t="n">
         <v>1</v>
@@ -16545,7 +16503,7 @@
         <v>1</v>
       </c>
       <c r="AD171" t="n">
-        <v>0.6485</v>
+        <v>0.6709999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -16583,7 +16541,7 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K172" t="n">
         <v>13</v>
@@ -16624,10 +16582,10 @@
         </is>
       </c>
       <c r="Y172" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="Z172" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="AA172" t="n">
         <v>0.67</v>
@@ -16639,7 +16597,7 @@
         <v>2</v>
       </c>
       <c r="AD172" t="n">
-        <v>0.6154999999999999</v>
+        <v>0.6385000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -16677,13 +16635,13 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K173" t="n">
         <v>13</v>
       </c>
       <c r="L173" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -16718,22 +16676,22 @@
         </is>
       </c>
       <c r="Y173" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="Z173" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
       <c r="AA173" t="n">
         <v>0.73</v>
       </c>
       <c r="AB173" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="AC173" t="n">
         <v>3</v>
       </c>
       <c r="AD173" t="n">
-        <v>0.619</v>
+        <v>0.4795</v>
       </c>
     </row>
     <row r="174">
@@ -16771,13 +16729,13 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K174" t="n">
         <v>13</v>
       </c>
       <c r="L174" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -16812,22 +16770,22 @@
         </is>
       </c>
       <c r="Y174" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="Z174" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="AA174" t="n">
         <v>0.92</v>
       </c>
       <c r="AB174" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="AC174" t="n">
         <v>1</v>
       </c>
       <c r="AD174" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="175">
@@ -16865,13 +16823,13 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K175" t="n">
         <v>13</v>
       </c>
       <c r="L175" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -16906,22 +16864,22 @@
         </is>
       </c>
       <c r="Y175" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="Z175" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="AA175" t="n">
         <v>0.51</v>
       </c>
       <c r="AB175" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="AC175" t="n">
         <v>2</v>
       </c>
       <c r="AD175" t="n">
-        <v>0.6345</v>
+        <v>0.5705</v>
       </c>
     </row>
     <row r="176">
@@ -16965,7 +16923,7 @@
         <v>13</v>
       </c>
       <c r="L176" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
@@ -17009,13 +16967,13 @@
         <v>0.29</v>
       </c>
       <c r="AB176" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC176" t="n">
         <v>3</v>
       </c>
       <c r="AD176" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.6554999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -17059,7 +17017,7 @@
         <v>13</v>
       </c>
       <c r="L177" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -17103,13 +17061,13 @@
         <v>0.7</v>
       </c>
       <c r="AB177" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC177" t="n">
         <v>2</v>
       </c>
       <c r="AD177" t="n">
-        <v>0.7045</v>
+        <v>0.6985</v>
       </c>
     </row>
     <row r="178">
@@ -17153,7 +17111,7 @@
         <v>13</v>
       </c>
       <c r="L178" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -17197,13 +17155,13 @@
         <v>0.93</v>
       </c>
       <c r="AB178" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC178" t="n">
         <v>1</v>
       </c>
       <c r="AD178" t="n">
-        <v>0.7244999999999999</v>
+        <v>0.7184999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -17241,13 +17199,13 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K179" t="n">
         <v>13</v>
       </c>
       <c r="L179" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -17291,13 +17249,13 @@
         <v>0.7</v>
       </c>
       <c r="AB179" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AC179" t="n">
         <v>3</v>
       </c>
       <c r="AD179" t="n">
-        <v>0.8875</v>
+        <v>0.8889999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -17335,13 +17293,13 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K180" t="n">
         <v>13</v>
       </c>
       <c r="L180" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -17385,13 +17343,13 @@
         <v>0.93</v>
       </c>
       <c r="AB180" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AC180" t="n">
         <v>1</v>
       </c>
       <c r="AD180" t="n">
-        <v>0.9335</v>
+        <v>0.9349999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -17429,13 +17387,13 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K181" t="n">
         <v>13</v>
       </c>
       <c r="L181" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
@@ -17473,19 +17431,19 @@
         <v>1</v>
       </c>
       <c r="Z181" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AA181" t="n">
         <v>0.86</v>
       </c>
       <c r="AB181" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AC181" t="n">
         <v>2</v>
       </c>
       <c r="AD181" t="n">
-        <v>0.9195</v>
+        <v>0.9175</v>
       </c>
     </row>
     <row r="182">
@@ -18093,7 +18051,7 @@
         <v>13</v>
       </c>
       <c r="L188" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
@@ -18187,7 +18145,7 @@
         <v>13</v>
       </c>
       <c r="L189" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -18231,13 +18189,13 @@
         <v>0.15</v>
       </c>
       <c r="AB189" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="AC189" t="n">
         <v>2</v>
       </c>
       <c r="AD189" t="n">
-        <v>0.6359999999999999</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="190">
@@ -18281,7 +18239,7 @@
         <v>13</v>
       </c>
       <c r="L190" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -18325,13 +18283,13 @@
         <v>0.51</v>
       </c>
       <c r="AB190" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="AC190" t="n">
         <v>1</v>
       </c>
       <c r="AD190" t="n">
-        <v>0.7219999999999999</v>
+        <v>0.7249999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -19218,14 +19176,14 @@
         <v>13</v>
       </c>
       <c r="K200" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L200" t="n">
         <v>25</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
@@ -19256,10 +19214,10 @@
         </is>
       </c>
       <c r="Y200" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="Z200" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -19271,7 +19229,7 @@
         <v>3</v>
       </c>
       <c r="AD200" t="n">
-        <v>0.5375</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="201">
@@ -19312,14 +19270,14 @@
         <v>13</v>
       </c>
       <c r="K201" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L201" t="n">
         <v>25</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
@@ -19350,10 +19308,10 @@
         </is>
       </c>
       <c r="Y201" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="Z201" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="AA201" t="n">
         <v>0.41</v>
@@ -19365,7 +19323,7 @@
         <v>2</v>
       </c>
       <c r="AD201" t="n">
-        <v>0.6415</v>
+        <v>0.6935</v>
       </c>
     </row>
     <row r="202">
@@ -19406,14 +19364,14 @@
         <v>13</v>
       </c>
       <c r="K202" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L202" t="n">
         <v>25</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -19444,10 +19402,10 @@
         </is>
       </c>
       <c r="Y202" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="Z202" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="AA202" t="n">
         <v>0.7</v>
@@ -19459,7 +19417,7 @@
         <v>1</v>
       </c>
       <c r="AD202" t="n">
-        <v>0.67</v>
+        <v>0.7284999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -19779,7 +19737,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K206" t="n">
         <v>13</v>
@@ -19820,10 +19778,10 @@
         </is>
       </c>
       <c r="Y206" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="Z206" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AA206" t="n">
         <v>0.78</v>
@@ -19835,7 +19793,7 @@
         <v>3</v>
       </c>
       <c r="AD206" t="n">
-        <v>0.6365000000000001</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="207">
@@ -19873,7 +19831,7 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K207" t="n">
         <v>13</v>
@@ -19914,10 +19872,10 @@
         </is>
       </c>
       <c r="Y207" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="Z207" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AA207" t="n">
         <v>1</v>
@@ -19929,7 +19887,7 @@
         <v>1</v>
       </c>
       <c r="AD207" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7194999999999999</v>
       </c>
     </row>
     <row r="208">
@@ -19967,7 +19925,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K208" t="n">
         <v>13</v>
@@ -20008,10 +19966,10 @@
         </is>
       </c>
       <c r="Y208" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="Z208" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AA208" t="n">
         <v>0.78</v>
@@ -20023,7 +19981,7 @@
         <v>2</v>
       </c>
       <c r="AD208" t="n">
-        <v>0.6785</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="209">
@@ -20354,7 +20312,7 @@
         </is>
       </c>
       <c r="O212" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
@@ -20386,10 +20344,10 @@
         </is>
       </c>
       <c r="Y212" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="Z212" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="AA212" t="n">
         <v>1</v>
@@ -20401,7 +20359,7 @@
         <v>1</v>
       </c>
       <c r="AD212" t="n">
-        <v>0.6735000000000001</v>
+        <v>0.5815</v>
       </c>
     </row>
     <row r="213">
@@ -20450,7 +20408,7 @@
         </is>
       </c>
       <c r="O213" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P213" t="inlineStr">
         <is>
@@ -20482,10 +20440,10 @@
         </is>
       </c>
       <c r="Y213" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="Z213" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="AA213" t="n">
         <v>0.64</v>
@@ -20497,7 +20455,7 @@
         <v>2</v>
       </c>
       <c r="AD213" t="n">
-        <v>0.6014999999999999</v>
+        <v>0.5275</v>
       </c>
     </row>
     <row r="214">
@@ -20546,7 +20504,7 @@
         </is>
       </c>
       <c r="O214" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P214" t="inlineStr">
         <is>
@@ -20578,10 +20536,10 @@
         </is>
       </c>
       <c r="Y214" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="Z214" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="AA214" t="n">
         <v>0.34</v>
@@ -20593,7 +20551,7 @@
         <v>3</v>
       </c>
       <c r="AD214" t="n">
-        <v>0.5415</v>
+        <v>0.4745</v>
       </c>
     </row>
     <row r="215">
@@ -20646,7 +20604,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr"/>
@@ -20742,7 +20700,7 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr"/>
@@ -20838,7 +20796,7 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr"/>
@@ -20930,7 +20888,7 @@
         </is>
       </c>
       <c r="O218" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="P218" t="inlineStr">
         <is>
@@ -20962,10 +20920,10 @@
         </is>
       </c>
       <c r="Y218" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="Z218" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="AA218" t="n">
         <v>1</v>
@@ -20977,7 +20935,7 @@
         <v>1</v>
       </c>
       <c r="AD218" t="n">
-        <v>0.792</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="219">
@@ -21026,7 +20984,7 @@
         </is>
       </c>
       <c r="O219" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
@@ -21058,10 +21016,10 @@
         </is>
       </c>
       <c r="Y219" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="Z219" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="AA219" t="n">
         <v>0.57</v>
@@ -21073,7 +21031,7 @@
         <v>3</v>
       </c>
       <c r="AD219" t="n">
-        <v>0.5545</v>
+        <v>0.5905</v>
       </c>
     </row>
     <row r="220">
@@ -21122,7 +21080,7 @@
         </is>
       </c>
       <c r="O220" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="P220" t="inlineStr">
         <is>
@@ -21154,10 +21112,10 @@
         </is>
       </c>
       <c r="Y220" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="Z220" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="AA220" t="n">
         <v>0.57</v>
@@ -21169,7 +21127,7 @@
         <v>2</v>
       </c>
       <c r="AD220" t="n">
-        <v>0.6174999999999999</v>
+        <v>0.6445</v>
       </c>
     </row>
     <row r="221">
@@ -21218,7 +21176,7 @@
         </is>
       </c>
       <c r="O221" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="P221" t="inlineStr">
         <is>
@@ -21250,10 +21208,10 @@
         </is>
       </c>
       <c r="Y221" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="Z221" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="AA221" t="n">
         <v>1</v>
@@ -21265,7 +21223,7 @@
         <v>1</v>
       </c>
       <c r="AD221" t="n">
-        <v>0.7785000000000001</v>
+        <v>0.8055</v>
       </c>
     </row>
     <row r="222">
@@ -21314,7 +21272,7 @@
         </is>
       </c>
       <c r="O222" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="P222" t="inlineStr">
         <is>
@@ -21346,10 +21304,10 @@
         </is>
       </c>
       <c r="Y222" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="Z222" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="AA222" t="n">
         <v>0.79</v>
@@ -21361,7 +21319,7 @@
         <v>2</v>
       </c>
       <c r="AD222" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6555</v>
       </c>
     </row>
     <row r="223">
@@ -21410,7 +21368,7 @@
         </is>
       </c>
       <c r="O223" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="P223" t="inlineStr">
         <is>
@@ -21442,10 +21400,10 @@
         </is>
       </c>
       <c r="Y223" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="Z223" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="AA223" t="n">
         <v>0.23</v>
@@ -21457,7 +21415,7 @@
         <v>3</v>
       </c>
       <c r="AD223" t="n">
-        <v>0.497</v>
+        <v>0.5239999999999999</v>
       </c>
     </row>
     <row r="224">
@@ -21506,7 +21464,7 @@
         </is>
       </c>
       <c r="O224" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P224" t="inlineStr">
         <is>
@@ -21538,7 +21496,7 @@
         </is>
       </c>
       <c r="Y224" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="Z224" t="n">
         <v>0</v>
@@ -21553,7 +21511,7 @@
         <v>1</v>
       </c>
       <c r="AD224" t="n">
-        <v>0.35</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="225">
@@ -21602,7 +21560,7 @@
         </is>
       </c>
       <c r="O225" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P225" t="inlineStr">
         <is>
@@ -21634,7 +21592,7 @@
         </is>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="Z225" t="n">
         <v>0</v>
@@ -21649,7 +21607,7 @@
         <v>3</v>
       </c>
       <c r="AD225" t="n">
-        <v>0.289</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="226">
@@ -21698,7 +21656,7 @@
         </is>
       </c>
       <c r="O226" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P226" t="inlineStr">
         <is>
@@ -21730,10 +21688,10 @@
         </is>
       </c>
       <c r="Y226" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA226" t="n">
         <v>0.52</v>
@@ -21745,7 +21703,7 @@
         <v>2</v>
       </c>
       <c r="AD226" t="n">
-        <v>0.32</v>
+        <v>0.3835</v>
       </c>
     </row>
     <row r="227">
@@ -22082,7 +22040,7 @@
         </is>
       </c>
       <c r="O230" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P230" t="inlineStr">
         <is>
@@ -22114,7 +22072,7 @@
         </is>
       </c>
       <c r="Y230" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Z230" t="n">
         <v>0</v>
@@ -22129,7 +22087,7 @@
         <v>1</v>
       </c>
       <c r="AD230" t="n">
-        <v>0.359</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="231">
@@ -22178,7 +22136,7 @@
         </is>
       </c>
       <c r="O231" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P231" t="inlineStr">
         <is>
@@ -22210,7 +22168,7 @@
         </is>
       </c>
       <c r="Y231" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Z231" t="n">
         <v>0</v>
@@ -22225,7 +22183,7 @@
         <v>3</v>
       </c>
       <c r="AD231" t="n">
-        <v>0.245</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="232">
@@ -22274,7 +22232,7 @@
         </is>
       </c>
       <c r="O232" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P232" t="inlineStr">
         <is>
@@ -22306,7 +22264,7 @@
         </is>
       </c>
       <c r="Y232" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="Z232" t="n">
         <v>0</v>
@@ -22321,7 +22279,7 @@
         <v>2</v>
       </c>
       <c r="AD232" t="n">
-        <v>0.2705</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="233">
@@ -22370,7 +22328,7 @@
         </is>
       </c>
       <c r="O233" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P233" t="inlineStr">
         <is>
@@ -22402,10 +22360,10 @@
         </is>
       </c>
       <c r="Y233" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="Z233" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="AA233" t="n">
         <v>1</v>
@@ -22417,7 +22375,7 @@
         <v>1</v>
       </c>
       <c r="AD233" t="n">
-        <v>0.6465</v>
+        <v>0.7440000000000001</v>
       </c>
     </row>
     <row r="234">
@@ -22466,7 +22424,7 @@
         </is>
       </c>
       <c r="O234" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P234" t="inlineStr">
         <is>
@@ -22498,10 +22456,10 @@
         </is>
       </c>
       <c r="Y234" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="Z234" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="AA234" t="n">
         <v>0.95</v>
@@ -22513,7 +22471,7 @@
         <v>2</v>
       </c>
       <c r="AD234" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.7220000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -22562,7 +22520,7 @@
         </is>
       </c>
       <c r="O235" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P235" t="inlineStr">
         <is>
@@ -22594,10 +22552,10 @@
         </is>
       </c>
       <c r="Y235" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="Z235" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AA235" t="n">
         <v>0.57</v>
@@ -22609,7 +22567,7 @@
         <v>3</v>
       </c>
       <c r="AD235" t="n">
-        <v>0.5545</v>
+        <v>0.6309999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -22658,7 +22616,7 @@
         </is>
       </c>
       <c r="O236" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P236" t="inlineStr">
         <is>
@@ -22754,7 +22712,7 @@
         </is>
       </c>
       <c r="O237" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P237" t="inlineStr">
         <is>
@@ -22786,10 +22744,10 @@
         </is>
       </c>
       <c r="Y237" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="Z237" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
         <v>0.29</v>
@@ -22801,7 +22759,7 @@
         <v>3</v>
       </c>
       <c r="AD237" t="n">
-        <v>0.3164999999999999</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="238">
@@ -22850,7 +22808,7 @@
         </is>
       </c>
       <c r="O238" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P238" t="inlineStr">
         <is>
@@ -22882,7 +22840,7 @@
         </is>
       </c>
       <c r="Y238" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="Z238" t="n">
         <v>0</v>
@@ -22897,7 +22855,7 @@
         <v>1</v>
       </c>
       <c r="AD238" t="n">
-        <v>0.4309999999999999</v>
+        <v>0.4069999999999999</v>
       </c>
     </row>
     <row r="239">
@@ -23522,7 +23480,7 @@
         </is>
       </c>
       <c r="O245" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="P245" t="inlineStr">
         <is>
@@ -23554,10 +23512,10 @@
         </is>
       </c>
       <c r="Y245" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="AA245" t="n">
         <v>1</v>
@@ -23569,7 +23527,7 @@
         <v>1</v>
       </c>
       <c r="AD245" t="n">
-        <v>0.669</v>
+        <v>0.4585</v>
       </c>
     </row>
     <row r="246">
@@ -23618,7 +23576,7 @@
         </is>
       </c>
       <c r="O246" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="P246" t="inlineStr">
         <is>
@@ -23650,10 +23608,10 @@
         </is>
       </c>
       <c r="Y246" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="Z246" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="AA246" t="n">
         <v>0.26</v>
@@ -23665,7 +23623,7 @@
         <v>2</v>
       </c>
       <c r="AD246" t="n">
-        <v>0.5765</v>
+        <v>0.4349999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -23714,7 +23672,7 @@
         </is>
       </c>
       <c r="O247" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="P247" t="inlineStr">
         <is>
@@ -23746,10 +23704,10 @@
         </is>
       </c>
       <c r="Y247" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="Z247" t="n">
-        <v>0.65</v>
+        <v>0.36</v>
       </c>
       <c r="AA247" t="n">
         <v>0.09</v>
@@ -23761,7 +23719,7 @@
         <v>3</v>
       </c>
       <c r="AD247" t="n">
-        <v>0.5289999999999999</v>
+        <v>0.3945</v>
       </c>
     </row>
     <row r="248">
@@ -23810,7 +23768,7 @@
         </is>
       </c>
       <c r="O248" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P248" t="inlineStr">
         <is>
@@ -23842,10 +23800,10 @@
         </is>
       </c>
       <c r="Y248" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA248" t="n">
         <v>0.83</v>
@@ -23857,7 +23815,7 @@
         <v>1</v>
       </c>
       <c r="AD248" t="n">
-        <v>0.4705</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="249">
@@ -23906,7 +23864,7 @@
         </is>
       </c>
       <c r="O249" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P249" t="inlineStr">
         <is>
@@ -24002,7 +23960,7 @@
         </is>
       </c>
       <c r="O250" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P250" t="inlineStr">
         <is>
@@ -24034,10 +23992,10 @@
         </is>
       </c>
       <c r="Y250" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="Z250" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA250" t="n">
         <v>0.7</v>
@@ -24049,7 +24007,7 @@
         <v>2</v>
       </c>
       <c r="AD250" t="n">
-        <v>0.4279999999999999</v>
+        <v>0.4705</v>
       </c>
     </row>
     <row r="251">
@@ -24098,7 +24056,7 @@
         </is>
       </c>
       <c r="O251" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P251" t="inlineStr">
         <is>
@@ -24133,7 +24091,7 @@
         <v>0</v>
       </c>
       <c r="Z251" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AA251" t="n">
         <v>1</v>
@@ -24145,7 +24103,7 @@
         <v>2</v>
       </c>
       <c r="AD251" t="n">
-        <v>0.35</v>
+        <v>0.4025</v>
       </c>
     </row>
     <row r="252">
@@ -24194,7 +24152,7 @@
         </is>
       </c>
       <c r="O252" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P252" t="inlineStr">
         <is>
@@ -24226,10 +24184,10 @@
         </is>
       </c>
       <c r="Y252" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AA252" t="n">
         <v>0.31</v>
@@ -24241,7 +24199,7 @@
         <v>3</v>
       </c>
       <c r="AD252" t="n">
-        <v>0.2795</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="253">
@@ -24290,7 +24248,7 @@
         </is>
       </c>
       <c r="O253" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P253" t="inlineStr">
         <is>
@@ -24322,10 +24280,10 @@
         </is>
       </c>
       <c r="Y253" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="Z253" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AA253" t="n">
         <v>0.63</v>
@@ -24337,7 +24295,7 @@
         <v>1</v>
       </c>
       <c r="AD253" t="n">
-        <v>0.3615</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="254">
@@ -24386,7 +24344,7 @@
         </is>
       </c>
       <c r="O254" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P254" t="inlineStr">
         <is>
@@ -24418,10 +24376,10 @@
         </is>
       </c>
       <c r="Y254" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="Z254" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="AA254" t="n">
         <v>1</v>
@@ -24433,7 +24391,7 @@
         <v>1</v>
       </c>
       <c r="AD254" t="n">
-        <v>0.6645</v>
+        <v>0.5665</v>
       </c>
     </row>
     <row r="255">
@@ -24482,7 +24440,7 @@
         </is>
       </c>
       <c r="O255" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P255" t="inlineStr">
         <is>
@@ -24514,10 +24472,10 @@
         </is>
       </c>
       <c r="Y255" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="Z255" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="AA255" t="n">
         <v>0.83</v>
@@ -24529,7 +24487,7 @@
         <v>3</v>
       </c>
       <c r="AD255" t="n">
-        <v>0.593</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="256">
@@ -24578,7 +24536,7 @@
         </is>
       </c>
       <c r="O256" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P256" t="inlineStr">
         <is>
@@ -24610,10 +24568,10 @@
         </is>
       </c>
       <c r="Y256" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="Z256" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="AA256" t="n">
         <v>0.73</v>
@@ -24625,7 +24583,7 @@
         <v>2</v>
       </c>
       <c r="AD256" t="n">
-        <v>0.615</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="257">
@@ -24674,11 +24632,11 @@
         </is>
       </c>
       <c r="O257" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr"/>
@@ -24706,10 +24664,10 @@
         </is>
       </c>
       <c r="Y257" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="Z257" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AA257" t="n">
         <v>0.89</v>
@@ -24721,7 +24679,7 @@
         <v>1</v>
       </c>
       <c r="AD257" t="n">
-        <v>0.9285000000000001</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="258">
@@ -24770,11 +24728,11 @@
         </is>
       </c>
       <c r="O258" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr"/>
@@ -24802,10 +24760,10 @@
         </is>
       </c>
       <c r="Y258" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="Z258" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA258" t="n">
         <v>0.52</v>
@@ -24817,7 +24775,7 @@
         <v>3</v>
       </c>
       <c r="AD258" t="n">
-        <v>0.7639999999999999</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="259">
@@ -24866,11 +24824,11 @@
         </is>
       </c>
       <c r="O259" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr"/>
@@ -24898,10 +24856,10 @@
         </is>
       </c>
       <c r="Y259" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="Z259" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA259" t="n">
         <v>0.65</v>
@@ -24913,7 +24871,7 @@
         <v>2</v>
       </c>
       <c r="AD259" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="260">
@@ -24966,7 +24924,7 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr"/>
@@ -25062,7 +25020,7 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr"/>
@@ -25158,7 +25116,7 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr"/>
@@ -25250,7 +25208,7 @@
         </is>
       </c>
       <c r="O263" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P263" t="inlineStr">
         <is>
@@ -25282,7 +25240,7 @@
         </is>
       </c>
       <c r="Y263" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
         <v>0</v>
@@ -25297,7 +25255,7 @@
         <v>1</v>
       </c>
       <c r="AD263" t="n">
-        <v>0.377</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="264">
@@ -25346,7 +25304,7 @@
         </is>
       </c>
       <c r="O264" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P264" t="inlineStr">
         <is>
@@ -25378,10 +25336,10 @@
         </is>
       </c>
       <c r="Y264" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="Z264" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA264" t="n">
         <v>0.38</v>
@@ -25393,7 +25351,7 @@
         <v>3</v>
       </c>
       <c r="AD264" t="n">
-        <v>0.291</v>
+        <v>0.2395</v>
       </c>
     </row>
     <row r="265">
@@ -25442,7 +25400,7 @@
         </is>
       </c>
       <c r="O265" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P265" t="inlineStr">
         <is>
@@ -25474,7 +25432,7 @@
         </is>
       </c>
       <c r="Y265" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="Z265" t="n">
         <v>0</v>
@@ -25489,7 +25447,7 @@
         <v>2</v>
       </c>
       <c r="AD265" t="n">
-        <v>0.3365</v>
+        <v>0.3095</v>
       </c>
     </row>
     <row r="266">
@@ -25538,7 +25496,7 @@
         </is>
       </c>
       <c r="O266" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="P266" t="inlineStr">
         <is>
@@ -25570,10 +25528,10 @@
         </is>
       </c>
       <c r="Y266" t="n">
-        <v>0.82</v>
+        <v>0.36</v>
       </c>
       <c r="Z266" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="AA266" t="n">
         <v>1</v>
@@ -25582,10 +25540,10 @@
         <v>1</v>
       </c>
       <c r="AC266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD266" t="n">
-        <v>0.89</v>
+        <v>0.5665</v>
       </c>
     </row>
     <row r="267">
@@ -25634,7 +25592,7 @@
         </is>
       </c>
       <c r="O267" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="P267" t="inlineStr">
         <is>
@@ -25666,10 +25624,10 @@
         </is>
       </c>
       <c r="Y267" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="Z267" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="AA267" t="n">
         <v>0.79</v>
@@ -25678,10 +25636,10 @@
         <v>0.68</v>
       </c>
       <c r="AC267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD267" t="n">
-        <v>0.833</v>
+        <v>0.5785</v>
       </c>
     </row>
     <row r="268">
@@ -25730,7 +25688,7 @@
         </is>
       </c>
       <c r="O268" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="P268" t="inlineStr">
         <is>
@@ -25762,10 +25720,10 @@
         </is>
       </c>
       <c r="Y268" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="Z268" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="AA268" t="n">
         <v>0.74</v>
@@ -25777,7 +25735,7 @@
         <v>3</v>
       </c>
       <c r="AD268" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.5595</v>
       </c>
     </row>
     <row r="269">
@@ -26114,7 +26072,7 @@
         </is>
       </c>
       <c r="O272" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="P272" t="inlineStr">
         <is>
@@ -26146,10 +26104,10 @@
         </is>
       </c>
       <c r="Y272" t="n">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="Z272" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="AA272" t="n">
         <v>1</v>
@@ -26161,7 +26119,7 @@
         <v>1</v>
       </c>
       <c r="AD272" t="n">
-        <v>0.9229999999999999</v>
+        <v>0.5485</v>
       </c>
     </row>
     <row r="273">
@@ -26210,7 +26168,7 @@
         </is>
       </c>
       <c r="O273" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="P273" t="inlineStr">
         <is>
@@ -26242,10 +26200,10 @@
         </is>
       </c>
       <c r="Y273" t="n">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="Z273" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="AA273" t="n">
         <v>0.74</v>
@@ -26254,10 +26212,10 @@
         <v>0.62</v>
       </c>
       <c r="AC273" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD273" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.4395</v>
       </c>
     </row>
     <row r="274">
@@ -26306,7 +26264,7 @@
         </is>
       </c>
       <c r="O274" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="P274" t="inlineStr">
         <is>
@@ -26338,10 +26296,10 @@
         </is>
       </c>
       <c r="Y274" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="Z274" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="AA274" t="n">
         <v>0.54</v>
@@ -26350,10 +26308,10 @@
         <v>0.34</v>
       </c>
       <c r="AC274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD274" t="n">
-        <v>0.7625</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="275">
@@ -26402,7 +26360,7 @@
         </is>
       </c>
       <c r="O275" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P275" t="inlineStr">
         <is>
@@ -26498,7 +26456,7 @@
         </is>
       </c>
       <c r="O276" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P276" t="inlineStr">
         <is>
@@ -26530,7 +26488,7 @@
         </is>
       </c>
       <c r="Y276" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="Z276" t="n">
         <v>0</v>
@@ -26545,7 +26503,7 @@
         <v>2</v>
       </c>
       <c r="AD276" t="n">
-        <v>0.313</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="277">
@@ -26594,7 +26552,7 @@
         </is>
       </c>
       <c r="O277" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P277" t="inlineStr">
         <is>
@@ -26626,10 +26584,10 @@
         </is>
       </c>
       <c r="Y277" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="Z277" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA277" t="n">
         <v>0.25</v>
@@ -26641,7 +26599,7 @@
         <v>3</v>
       </c>
       <c r="AD277" t="n">
-        <v>0.256</v>
+        <v>0.1865</v>
       </c>
     </row>
     <row r="278">
@@ -27554,7 +27512,7 @@
         </is>
       </c>
       <c r="O287" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P287" t="inlineStr">
         <is>
@@ -27586,10 +27544,10 @@
         </is>
       </c>
       <c r="Y287" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="Z287" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AA287" t="n">
         <v>1</v>
@@ -27601,7 +27559,7 @@
         <v>1</v>
       </c>
       <c r="AD287" t="n">
-        <v>0.5315</v>
+        <v>0.4490000000000001</v>
       </c>
     </row>
     <row r="288">
@@ -27650,7 +27608,7 @@
         </is>
       </c>
       <c r="O288" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P288" t="inlineStr">
         <is>
@@ -27682,10 +27640,10 @@
         </is>
       </c>
       <c r="Y288" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="Z288" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AA288" t="n">
         <v>0.51</v>
@@ -27697,7 +27655,7 @@
         <v>3</v>
       </c>
       <c r="AD288" t="n">
-        <v>0.3345</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="289">
@@ -27746,7 +27704,7 @@
         </is>
       </c>
       <c r="O289" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P289" t="inlineStr">
         <is>
@@ -27778,10 +27736,10 @@
         </is>
       </c>
       <c r="Y289" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="Z289" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AA289" t="n">
         <v>0.79</v>
@@ -27793,7 +27751,7 @@
         <v>2</v>
       </c>
       <c r="AD289" t="n">
-        <v>0.4415</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="290">
@@ -28422,7 +28380,7 @@
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="Q296" t="inlineStr"/>
@@ -28518,7 +28476,7 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="Q297" t="inlineStr"/>
@@ -28614,7 +28572,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr"/>
@@ -29570,11 +29528,11 @@
         </is>
       </c>
       <c r="O308" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="Q308" t="inlineStr"/>
@@ -29602,10 +29560,10 @@
         </is>
       </c>
       <c r="Y308" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Z308" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="AA308" t="n">
         <v>1</v>
@@ -29614,10 +29572,10 @@
         <v>1</v>
       </c>
       <c r="AC308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD308" t="n">
-        <v>0.7245</v>
+        <v>0.6855000000000001</v>
       </c>
     </row>
     <row r="309">
@@ -29666,11 +29624,11 @@
         </is>
       </c>
       <c r="O309" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr"/>
@@ -29698,10 +29656,10 @@
         </is>
       </c>
       <c r="Y309" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="Z309" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="AA309" t="n">
         <v>0.85</v>
@@ -29710,10 +29668,10 @@
         <v>0.67</v>
       </c>
       <c r="AC309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD309" t="n">
-        <v>0.7170000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -29762,11 +29720,11 @@
         </is>
       </c>
       <c r="O310" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr"/>
@@ -29794,10 +29752,10 @@
         </is>
       </c>
       <c r="Y310" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="Z310" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA310" t="n">
         <v>0.71</v>
@@ -29809,7 +29767,7 @@
         <v>3</v>
       </c>
       <c r="AD310" t="n">
-        <v>0.653</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="311">
@@ -30146,7 +30104,7 @@
         </is>
       </c>
       <c r="O314" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P314" t="inlineStr">
         <is>
@@ -30178,10 +30136,10 @@
         </is>
       </c>
       <c r="Y314" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Z314" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="AA314" t="n">
         <v>0.51</v>
@@ -30193,7 +30151,7 @@
         <v>3</v>
       </c>
       <c r="AD314" t="n">
-        <v>0.422</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="315">
@@ -30242,7 +30200,7 @@
         </is>
       </c>
       <c r="O315" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P315" t="inlineStr">
         <is>
@@ -30274,10 +30232,10 @@
         </is>
       </c>
       <c r="Y315" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Z315" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="AA315" t="n">
         <v>0.63</v>
@@ -30289,7 +30247,7 @@
         <v>2</v>
       </c>
       <c r="AD315" t="n">
-        <v>0.4475</v>
+        <v>0.5365</v>
       </c>
     </row>
     <row r="316">
@@ -30338,7 +30296,7 @@
         </is>
       </c>
       <c r="O316" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P316" t="inlineStr">
         <is>
@@ -30370,10 +30328,10 @@
         </is>
       </c>
       <c r="Y316" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Z316" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="AA316" t="n">
         <v>0.7</v>
@@ -30385,7 +30343,7 @@
         <v>1</v>
       </c>
       <c r="AD316" t="n">
-        <v>0.4775</v>
+        <v>0.5595</v>
       </c>
     </row>
     <row r="317">
@@ -30434,7 +30392,7 @@
         </is>
       </c>
       <c r="O317" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="P317" t="inlineStr">
         <is>
@@ -30466,10 +30424,10 @@
         </is>
       </c>
       <c r="Y317" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="Z317" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="AA317" t="n">
         <v>0.96</v>
@@ -30481,7 +30439,7 @@
         <v>1</v>
       </c>
       <c r="AD317" t="n">
-        <v>0.724</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="318">
@@ -30530,7 +30488,7 @@
         </is>
       </c>
       <c r="O318" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>
@@ -30562,10 +30520,10 @@
         </is>
       </c>
       <c r="Y318" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="Z318" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="AA318" t="n">
         <v>0.91</v>
@@ -30577,7 +30535,7 @@
         <v>2</v>
       </c>
       <c r="AD318" t="n">
-        <v>0.702</v>
+        <v>0.9195</v>
       </c>
     </row>
     <row r="319">
@@ -30626,7 +30584,7 @@
         </is>
       </c>
       <c r="O319" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="P319" t="inlineStr">
         <is>
@@ -30658,10 +30616,10 @@
         </is>
       </c>
       <c r="Y319" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="Z319" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="AA319" t="n">
         <v>0.78</v>
@@ -30673,7 +30631,7 @@
         <v>3</v>
       </c>
       <c r="AD319" t="n">
-        <v>0.649</v>
+        <v>0.8665</v>
       </c>
     </row>
     <row r="320">
@@ -30722,7 +30680,7 @@
         </is>
       </c>
       <c r="O320" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P320" t="inlineStr">
         <is>
@@ -30818,7 +30776,7 @@
         </is>
       </c>
       <c r="O321" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P321" t="inlineStr">
         <is>
@@ -30862,7 +30820,7 @@
         <v>0.75</v>
       </c>
       <c r="AC321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD321" t="n">
         <v>0.2785</v>
@@ -30914,7 +30872,7 @@
         </is>
       </c>
       <c r="O322" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P322" t="inlineStr">
         <is>
@@ -30946,7 +30904,7 @@
         </is>
       </c>
       <c r="Y322" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="Z322" t="n">
         <v>0</v>
@@ -30958,10 +30916,10 @@
         <v>0.25</v>
       </c>
       <c r="AC322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD322" t="n">
-        <v>0.2755</v>
+        <v>0.2905</v>
       </c>
     </row>
     <row r="323">
@@ -31298,11 +31256,11 @@
         </is>
       </c>
       <c r="O326" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr"/>
@@ -31330,10 +31288,10 @@
         </is>
       </c>
       <c r="Y326" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="Z326" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="AA326" t="n">
         <v>0.9399999999999999</v>
@@ -31345,7 +31303,7 @@
         <v>1</v>
       </c>
       <c r="AD326" t="n">
-        <v>0.661</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="327">
@@ -31394,11 +31352,11 @@
         </is>
       </c>
       <c r="O327" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr"/>
@@ -31426,10 +31384,10 @@
         </is>
       </c>
       <c r="Y327" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="Z327" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="AA327" t="n">
         <v>0.82</v>
@@ -31441,7 +31399,7 @@
         <v>2</v>
       </c>
       <c r="AD327" t="n">
-        <v>0.61</v>
+        <v>0.7110000000000001</v>
       </c>
     </row>
     <row r="328">
@@ -31490,11 +31448,11 @@
         </is>
       </c>
       <c r="O328" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="Q328" t="inlineStr"/>
@@ -31522,10 +31480,10 @@
         </is>
       </c>
       <c r="Y328" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z328" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="AA328" t="n">
         <v>0.58</v>
@@ -31537,7 +31495,7 @@
         <v>3</v>
       </c>
       <c r="AD328" t="n">
-        <v>0.289</v>
+        <v>0.426</v>
       </c>
     </row>
     <row r="329">
@@ -32162,7 +32120,7 @@
         </is>
       </c>
       <c r="O335" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P335" t="inlineStr">
         <is>
@@ -32194,7 +32152,7 @@
         </is>
       </c>
       <c r="Y335" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="Z335" t="n">
         <v>0</v>
@@ -32209,7 +32167,7 @@
         <v>1</v>
       </c>
       <c r="AD335" t="n">
-        <v>0.554</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="336">
@@ -32258,7 +32216,7 @@
         </is>
       </c>
       <c r="O336" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P336" t="inlineStr">
         <is>
@@ -32290,7 +32248,7 @@
         </is>
       </c>
       <c r="Y336" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="Z336" t="n">
         <v>0</v>
@@ -32305,7 +32263,7 @@
         <v>2</v>
       </c>
       <c r="AD336" t="n">
-        <v>0.357</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="337">
@@ -32354,7 +32312,7 @@
         </is>
       </c>
       <c r="O337" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P337" t="inlineStr">
         <is>
@@ -32386,10 +32344,10 @@
         </is>
       </c>
       <c r="Y337" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="Z337" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA337" t="n">
         <v>0.43</v>
@@ -32401,7 +32359,7 @@
         <v>3</v>
       </c>
       <c r="AD337" t="n">
-        <v>0.3415</v>
+        <v>0.3080000000000001</v>
       </c>
     </row>
     <row r="338">
@@ -32450,7 +32408,7 @@
         </is>
       </c>
       <c r="O338" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="P338" t="inlineStr">
         <is>
@@ -32482,10 +32440,10 @@
         </is>
       </c>
       <c r="Y338" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="Z338" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AA338" t="n">
         <v>1</v>
@@ -32497,7 +32455,7 @@
         <v>1</v>
       </c>
       <c r="AD338" t="n">
-        <v>0.7560000000000001</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="339">
@@ -32546,7 +32504,7 @@
         </is>
       </c>
       <c r="O339" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="P339" t="inlineStr">
         <is>
@@ -32578,10 +32536,10 @@
         </is>
       </c>
       <c r="Y339" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="Z339" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AA339" t="n">
         <v>0.78</v>
@@ -32593,7 +32551,7 @@
         <v>2</v>
       </c>
       <c r="AD339" t="n">
-        <v>0.6625000000000001</v>
+        <v>0.6460000000000001</v>
       </c>
     </row>
     <row r="340">
@@ -32642,7 +32600,7 @@
         </is>
       </c>
       <c r="O340" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="P340" t="inlineStr">
         <is>
@@ -32674,10 +32632,10 @@
         </is>
       </c>
       <c r="Y340" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="Z340" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA340" t="n">
         <v>0.55</v>
@@ -32689,7 +32647,7 @@
         <v>3</v>
       </c>
       <c r="AD340" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5505</v>
       </c>
     </row>
     <row r="341">
@@ -32738,7 +32696,7 @@
         </is>
       </c>
       <c r="O341" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="P341" t="inlineStr">
         <is>
@@ -32770,10 +32728,10 @@
         </is>
       </c>
       <c r="Y341" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Z341" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="AA341" t="n">
         <v>1</v>
@@ -32785,7 +32743,7 @@
         <v>1</v>
       </c>
       <c r="AD341" t="n">
-        <v>0.8384999999999999</v>
+        <v>0.7065</v>
       </c>
     </row>
     <row r="342">
@@ -32834,7 +32792,7 @@
         </is>
       </c>
       <c r="O342" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="P342" t="inlineStr">
         <is>
@@ -32866,10 +32824,10 @@
         </is>
       </c>
       <c r="Y342" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Z342" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="AA342" t="n">
         <v>0.79</v>
@@ -32881,7 +32839,7 @@
         <v>2</v>
       </c>
       <c r="AD342" t="n">
-        <v>0.7484999999999999</v>
+        <v>0.6164999999999999</v>
       </c>
     </row>
     <row r="343">
@@ -32930,7 +32888,7 @@
         </is>
       </c>
       <c r="O343" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="P343" t="inlineStr">
         <is>
@@ -32962,10 +32920,10 @@
         </is>
       </c>
       <c r="Y343" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Z343" t="n">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AA343" t="n">
         <v>0.38</v>
@@ -32977,7 +32935,7 @@
         <v>3</v>
       </c>
       <c r="AD343" t="n">
-        <v>0.5974999999999999</v>
+        <v>0.4655</v>
       </c>
     </row>
     <row r="344">
@@ -33026,11 +32984,11 @@
         </is>
       </c>
       <c r="O344" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7pm</t>
         </is>
       </c>
       <c r="Q344" t="inlineStr"/>
@@ -33058,10 +33016,10 @@
         </is>
       </c>
       <c r="Y344" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="Z344" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="AA344" t="n">
         <v>1</v>
@@ -33073,7 +33031,7 @@
         <v>1</v>
       </c>
       <c r="AD344" t="n">
-        <v>0.7065</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="345">
@@ -33122,11 +33080,11 @@
         </is>
       </c>
       <c r="O345" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P345" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7pm</t>
         </is>
       </c>
       <c r="Q345" t="inlineStr"/>
@@ -33154,10 +33112,10 @@
         </is>
       </c>
       <c r="Y345" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="Z345" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="AA345" t="n">
         <v>0.85</v>
@@ -33169,7 +33127,7 @@
         <v>2</v>
       </c>
       <c r="AD345" t="n">
-        <v>0.627</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="346">
@@ -33218,11 +33176,11 @@
         </is>
       </c>
       <c r="O346" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P346" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7pm</t>
         </is>
       </c>
       <c r="Q346" t="inlineStr"/>
@@ -33250,10 +33208,10 @@
         </is>
       </c>
       <c r="Y346" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="Z346" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA346" t="n">
         <v>0.76</v>
@@ -33265,7 +33223,7 @@
         <v>3</v>
       </c>
       <c r="AD346" t="n">
-        <v>0.5835</v>
+        <v>0.6165</v>
       </c>
     </row>
     <row r="347">
@@ -33314,7 +33272,7 @@
         </is>
       </c>
       <c r="O347" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="P347" t="inlineStr">
         <is>
@@ -33346,10 +33304,10 @@
         </is>
       </c>
       <c r="Y347" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="Z347" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="AA347" t="n">
         <v>1</v>
@@ -33361,7 +33319,7 @@
         <v>1</v>
       </c>
       <c r="AD347" t="n">
-        <v>0.7395</v>
+        <v>0.7065</v>
       </c>
     </row>
     <row r="348">
@@ -33410,7 +33368,7 @@
         </is>
       </c>
       <c r="O348" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="P348" t="inlineStr">
         <is>
@@ -33442,10 +33400,10 @@
         </is>
       </c>
       <c r="Y348" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="Z348" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="AA348" t="n">
         <v>0.7</v>
@@ -33457,7 +33415,7 @@
         <v>2</v>
       </c>
       <c r="AD348" t="n">
-        <v>0.615</v>
+        <v>0.582</v>
       </c>
     </row>
     <row r="349">
@@ -33506,7 +33464,7 @@
         </is>
       </c>
       <c r="O349" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="P349" t="inlineStr">
         <is>
@@ -33538,10 +33496,10 @@
         </is>
       </c>
       <c r="Y349" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="Z349" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="AA349" t="n">
         <v>0.43</v>
@@ -33553,7 +33511,7 @@
         <v>3</v>
       </c>
       <c r="AD349" t="n">
-        <v>0.537</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="350">
@@ -33602,7 +33560,7 @@
         </is>
       </c>
       <c r="O350" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P350" t="inlineStr">
         <is>
@@ -33646,7 +33604,7 @@
         <v>1</v>
       </c>
       <c r="AC350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD350" t="n">
         <v>0.35</v>
@@ -33698,7 +33656,7 @@
         </is>
       </c>
       <c r="O351" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P351" t="inlineStr">
         <is>
@@ -33730,7 +33688,7 @@
         </is>
       </c>
       <c r="Y351" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="Z351" t="n">
         <v>0</v>
@@ -33745,7 +33703,7 @@
         <v>1</v>
       </c>
       <c r="AD351" t="n">
-        <v>0.3615</v>
+        <v>0.3945</v>
       </c>
     </row>
     <row r="352">
@@ -33794,7 +33752,7 @@
         </is>
       </c>
       <c r="O352" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P352" t="inlineStr">
         <is>
@@ -33826,10 +33784,10 @@
         </is>
       </c>
       <c r="Y352" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="Z352" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA352" t="n">
         <v>0.43</v>
@@ -33838,10 +33796,10 @@
         <v>0.31</v>
       </c>
       <c r="AC352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD352" t="n">
-        <v>0.2945</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="353">
@@ -33890,7 +33848,7 @@
         </is>
       </c>
       <c r="O353" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P353" t="inlineStr">
         <is>
@@ -33922,10 +33880,10 @@
         </is>
       </c>
       <c r="Y353" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Z353" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AA353" t="n">
         <v>0.78</v>
@@ -33937,7 +33895,7 @@
         <v>1</v>
       </c>
       <c r="AD353" t="n">
-        <v>0.8780000000000001</v>
+        <v>0.8645</v>
       </c>
     </row>
     <row r="354">
@@ -33986,7 +33944,7 @@
         </is>
       </c>
       <c r="O354" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P354" t="inlineStr">
         <is>
@@ -34018,10 +33976,10 @@
         </is>
       </c>
       <c r="Y354" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Z354" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA354" t="n">
         <v>0.55</v>
@@ -34033,7 +33991,7 @@
         <v>2</v>
       </c>
       <c r="AD354" t="n">
-        <v>0.7474999999999999</v>
+        <v>0.7339999999999999</v>
       </c>
     </row>
     <row r="355">
@@ -34082,7 +34040,7 @@
         </is>
       </c>
       <c r="O355" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P355" t="inlineStr">
         <is>
@@ -34114,10 +34072,10 @@
         </is>
       </c>
       <c r="Y355" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="Z355" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA355" t="n">
         <v>0.55</v>
@@ -34129,7 +34087,7 @@
         <v>3</v>
       </c>
       <c r="AD355" t="n">
-        <v>0.7174999999999999</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="356">
@@ -34178,7 +34136,7 @@
         </is>
       </c>
       <c r="O356" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P356" t="inlineStr">
         <is>
@@ -34210,10 +34168,10 @@
         </is>
       </c>
       <c r="Y356" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="Z356" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AA356" t="n">
         <v>0.78</v>
@@ -34225,7 +34183,7 @@
         <v>1</v>
       </c>
       <c r="AD356" t="n">
-        <v>0.857</v>
+        <v>0.8435000000000001</v>
       </c>
     </row>
     <row r="357">
@@ -34274,7 +34232,7 @@
         </is>
       </c>
       <c r="O357" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P357" t="inlineStr">
         <is>
@@ -34306,10 +34264,10 @@
         </is>
       </c>
       <c r="Y357" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="Z357" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA357" t="n">
         <v>0.59</v>
@@ -34321,7 +34279,7 @@
         <v>2</v>
       </c>
       <c r="AD357" t="n">
-        <v>0.754</v>
+        <v>0.7404999999999999</v>
       </c>
     </row>
     <row r="358">
@@ -34370,7 +34328,7 @@
         </is>
       </c>
       <c r="O358" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P358" t="inlineStr">
         <is>
@@ -34402,10 +34360,10 @@
         </is>
       </c>
       <c r="Y358" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="Z358" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AA358" t="n">
         <v>0.63</v>
@@ -34417,7 +34375,7 @@
         <v>3</v>
       </c>
       <c r="AD358" t="n">
-        <v>0.732</v>
+        <v>0.7124999999999999</v>
       </c>
     </row>
     <row r="359">
@@ -34466,7 +34424,7 @@
         </is>
       </c>
       <c r="O359" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P359" t="inlineStr">
         <is>
@@ -34498,10 +34456,10 @@
         </is>
       </c>
       <c r="Y359" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z359" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA359" t="n">
         <v>0.78</v>
@@ -34513,7 +34471,7 @@
         <v>1</v>
       </c>
       <c r="AD359" t="n">
-        <v>0.4305</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="360">
@@ -34562,7 +34520,7 @@
         </is>
       </c>
       <c r="O360" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P360" t="inlineStr">
         <is>
@@ -34594,7 +34552,7 @@
         </is>
       </c>
       <c r="Y360" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z360" t="n">
         <v>0</v>
@@ -34609,7 +34567,7 @@
         <v>2</v>
       </c>
       <c r="AD360" t="n">
-        <v>0.359</v>
+        <v>0.3800000000000001</v>
       </c>
     </row>
     <row r="361">
@@ -34658,7 +34616,7 @@
         </is>
       </c>
       <c r="O361" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P361" t="inlineStr">
         <is>
@@ -34690,7 +34648,7 @@
         </is>
       </c>
       <c r="Y361" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Z361" t="n">
         <v>0</v>
@@ -34705,7 +34663,7 @@
         <v>3</v>
       </c>
       <c r="AD361" t="n">
-        <v>0.1685</v>
+        <v>0.1955</v>
       </c>
     </row>
     <row r="362">
@@ -34754,11 +34712,11 @@
         </is>
       </c>
       <c r="O362" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="P362" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8am</t>
         </is>
       </c>
       <c r="Q362" t="inlineStr"/>
@@ -34786,10 +34744,10 @@
         </is>
       </c>
       <c r="Y362" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Z362" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA362" t="n">
         <v>1</v>
@@ -34801,7 +34759,7 @@
         <v>1</v>
       </c>
       <c r="AD362" t="n">
-        <v>0.8145000000000001</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="363">
@@ -34850,11 +34808,11 @@
         </is>
       </c>
       <c r="O363" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="P363" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8am</t>
         </is>
       </c>
       <c r="Q363" t="inlineStr"/>
@@ -34882,10 +34840,10 @@
         </is>
       </c>
       <c r="Y363" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Z363" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA363" t="n">
         <v>0.78</v>
@@ -34897,7 +34855,7 @@
         <v>2</v>
       </c>
       <c r="AD363" t="n">
-        <v>0.7210000000000001</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="364">
@@ -34946,11 +34904,11 @@
         </is>
       </c>
       <c r="O364" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="P364" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8am</t>
         </is>
       </c>
       <c r="Q364" t="inlineStr"/>
@@ -34978,10 +34936,10 @@
         </is>
       </c>
       <c r="Y364" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Z364" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA364" t="n">
         <v>0.47</v>
@@ -34993,7 +34951,7 @@
         <v>3</v>
       </c>
       <c r="AD364" t="n">
-        <v>0.602</v>
+        <v>0.5885</v>
       </c>
     </row>
     <row r="365">
@@ -35042,7 +35000,7 @@
         </is>
       </c>
       <c r="O365" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P365" t="inlineStr">
         <is>
@@ -35074,10 +35032,10 @@
         </is>
       </c>
       <c r="Y365" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="Z365" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA365" t="n">
         <v>0.78</v>
@@ -35089,7 +35047,7 @@
         <v>1</v>
       </c>
       <c r="AD365" t="n">
-        <v>0.5030000000000001</v>
+        <v>0.4455000000000001</v>
       </c>
     </row>
     <row r="366">
@@ -35138,7 +35096,7 @@
         </is>
       </c>
       <c r="O366" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P366" t="inlineStr">
         <is>
@@ -35170,7 +35128,7 @@
         </is>
       </c>
       <c r="Y366" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="Z366" t="n">
         <v>0</v>
@@ -35185,7 +35143,7 @@
         <v>2</v>
       </c>
       <c r="AD366" t="n">
-        <v>0.3685</v>
+        <v>0.3355</v>
       </c>
     </row>
     <row r="367">
@@ -35234,7 +35192,7 @@
         </is>
       </c>
       <c r="O367" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P367" t="inlineStr">
         <is>
@@ -35906,7 +35864,7 @@
         </is>
       </c>
       <c r="O374" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P374" t="inlineStr">
         <is>
@@ -35938,10 +35896,10 @@
         </is>
       </c>
       <c r="Y374" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="Z374" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="AA374" t="n">
         <v>1</v>
@@ -35953,7 +35911,7 @@
         <v>1</v>
       </c>
       <c r="AD374" t="n">
-        <v>0.5045000000000001</v>
+        <v>0.5935</v>
       </c>
     </row>
     <row r="375">
@@ -36002,7 +35960,7 @@
         </is>
       </c>
       <c r="O375" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P375" t="inlineStr">
         <is>
@@ -36034,10 +35992,10 @@
         </is>
       </c>
       <c r="Y375" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="Z375" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AA375" t="n">
         <v>0.46</v>
@@ -36049,7 +36007,7 @@
         <v>2</v>
       </c>
       <c r="AD375" t="n">
-        <v>0.4625</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="376">
@@ -36098,7 +36056,7 @@
         </is>
       </c>
       <c r="O376" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P376" t="inlineStr">
         <is>
@@ -36130,10 +36088,10 @@
         </is>
       </c>
       <c r="Y376" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="Z376" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AA376" t="n">
         <v>0.21</v>
@@ -36145,7 +36103,7 @@
         <v>3</v>
       </c>
       <c r="AD376" t="n">
-        <v>0.393</v>
+        <v>0.4605</v>
       </c>
     </row>
     <row r="377">
@@ -36194,7 +36152,7 @@
         </is>
       </c>
       <c r="O377" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="P377" t="inlineStr">
         <is>
@@ -36229,7 +36187,7 @@
         <v>0.85</v>
       </c>
       <c r="Z377" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AA377" t="n">
         <v>1</v>
@@ -36241,7 +36199,7 @@
         <v>1</v>
       </c>
       <c r="AD377" t="n">
-        <v>0.801</v>
+        <v>0.8045000000000001</v>
       </c>
     </row>
     <row r="378">
@@ -36290,7 +36248,7 @@
         </is>
       </c>
       <c r="O378" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="P378" t="inlineStr">
         <is>
@@ -36322,10 +36280,10 @@
         </is>
       </c>
       <c r="Y378" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="Z378" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AA378" t="n">
         <v>0.74</v>
@@ -36337,7 +36295,7 @@
         <v>3</v>
       </c>
       <c r="AD378" t="n">
-        <v>0.509</v>
+        <v>0.5215</v>
       </c>
     </row>
     <row r="379">
@@ -36386,7 +36344,7 @@
         </is>
       </c>
       <c r="O379" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="P379" t="inlineStr">
         <is>
@@ -36421,7 +36379,7 @@
         <v>0.85</v>
       </c>
       <c r="Z379" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="AA379" t="n">
         <v>0.59</v>
@@ -36433,7 +36391,7 @@
         <v>2</v>
       </c>
       <c r="AD379" t="n">
-        <v>0.6275000000000001</v>
+        <v>0.6345000000000001</v>
       </c>
     </row>
     <row r="380">
@@ -36482,7 +36440,7 @@
         </is>
       </c>
       <c r="O380" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="P380" t="inlineStr">
         <is>
@@ -36514,10 +36472,10 @@
         </is>
       </c>
       <c r="Y380" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="Z380" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="AA380" t="n">
         <v>1</v>
@@ -36529,7 +36487,7 @@
         <v>1</v>
       </c>
       <c r="AD380" t="n">
-        <v>0.828</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="381">
@@ -36578,7 +36536,7 @@
         </is>
       </c>
       <c r="O381" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="P381" t="inlineStr">
         <is>
@@ -36610,10 +36568,10 @@
         </is>
       </c>
       <c r="Y381" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="Z381" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA381" t="n">
         <v>0.51</v>
@@ -36625,7 +36583,7 @@
         <v>2</v>
       </c>
       <c r="AD381" t="n">
-        <v>0.676</v>
+        <v>0.6355000000000001</v>
       </c>
     </row>
     <row r="382">
@@ -36674,7 +36632,7 @@
         </is>
       </c>
       <c r="O382" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="P382" t="inlineStr">
         <is>
@@ -36706,10 +36664,10 @@
         </is>
       </c>
       <c r="Y382" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="Z382" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="AA382" t="n">
         <v>0.59</v>
@@ -36721,7 +36679,7 @@
         <v>3</v>
       </c>
       <c r="AD382" t="n">
-        <v>0.6619999999999999</v>
+        <v>0.6214999999999999</v>
       </c>
     </row>
     <row r="383">
@@ -37058,7 +37016,7 @@
         </is>
       </c>
       <c r="O386" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -37090,10 +37048,10 @@
         </is>
       </c>
       <c r="Y386" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="Z386" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AA386" t="n">
         <v>1</v>
@@ -37105,7 +37063,7 @@
         <v>1</v>
       </c>
       <c r="AD386" t="n">
-        <v>0.777</v>
+        <v>0.7635</v>
       </c>
     </row>
     <row r="387">
@@ -37154,7 +37112,7 @@
         </is>
       </c>
       <c r="O387" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -37186,10 +37144,10 @@
         </is>
       </c>
       <c r="Y387" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="Z387" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AA387" t="n">
         <v>0.71</v>
@@ -37201,7 +37159,7 @@
         <v>2</v>
       </c>
       <c r="AD387" t="n">
-        <v>0.581</v>
+        <v>0.5644999999999999</v>
       </c>
     </row>
     <row r="388">
@@ -37250,7 +37208,7 @@
         </is>
       </c>
       <c r="O388" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="P388" t="inlineStr">
         <is>
@@ -37282,10 +37240,10 @@
         </is>
       </c>
       <c r="Y388" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="Z388" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AA388" t="n">
         <v>0.53</v>
@@ -37297,7 +37255,7 @@
         <v>3</v>
       </c>
       <c r="AD388" t="n">
-        <v>0.5675</v>
+        <v>0.5539999999999999</v>
       </c>
     </row>
     <row r="389">
@@ -37346,7 +37304,7 @@
         </is>
       </c>
       <c r="O389" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="P389" t="inlineStr">
         <is>
@@ -37378,10 +37336,10 @@
         </is>
       </c>
       <c r="Y389" t="n">
-        <v>0.34</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z389" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="AA389" t="n">
         <v>1</v>
@@ -37390,10 +37348,10 @@
         <v>1</v>
       </c>
       <c r="AC389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD389" t="n">
-        <v>0.5045000000000001</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="390">
@@ -37442,7 +37400,7 @@
         </is>
       </c>
       <c r="O390" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -37474,10 +37432,10 @@
         </is>
       </c>
       <c r="Y390" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="Z390" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="AA390" t="n">
         <v>0.74</v>
@@ -37486,10 +37444,10 @@
         <v>0.62</v>
       </c>
       <c r="AC390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD390" t="n">
-        <v>0.5125</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="391">
@@ -37538,7 +37496,7 @@
         </is>
       </c>
       <c r="O391" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -37570,10 +37528,10 @@
         </is>
       </c>
       <c r="Y391" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="Z391" t="n">
-        <v>0.21</v>
+        <v>0.65</v>
       </c>
       <c r="AA391" t="n">
         <v>0.29</v>
@@ -37585,7 +37543,7 @@
         <v>3</v>
       </c>
       <c r="AD391" t="n">
-        <v>0.373</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="392">
@@ -37922,7 +37880,7 @@
         </is>
       </c>
       <c r="O395" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="P395" t="inlineStr">
         <is>
@@ -37954,10 +37912,10 @@
         </is>
       </c>
       <c r="Y395" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="Z395" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="AA395" t="n">
         <v>1</v>
@@ -37969,7 +37927,7 @@
         <v>1</v>
       </c>
       <c r="AD395" t="n">
-        <v>0.8145000000000001</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="396">
@@ -38018,7 +37976,7 @@
         </is>
       </c>
       <c r="O396" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="P396" t="inlineStr">
         <is>
@@ -38050,10 +38008,10 @@
         </is>
       </c>
       <c r="Y396" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="Z396" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="AA396" t="n">
         <v>0.74</v>
@@ -38065,7 +38023,7 @@
         <v>3</v>
       </c>
       <c r="AD396" t="n">
-        <v>0.5345</v>
+        <v>0.5599999999999999</v>
       </c>
     </row>
     <row r="397">
@@ -38114,7 +38072,7 @@
         </is>
       </c>
       <c r="O397" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -38146,10 +38104,10 @@
         </is>
       </c>
       <c r="Y397" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="Z397" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="AA397" t="n">
         <v>0.63</v>
@@ -38161,7 +38119,7 @@
         <v>2</v>
       </c>
       <c r="AD397" t="n">
-        <v>0.655</v>
+        <v>0.6685000000000001</v>
       </c>
     </row>
     <row r="398">
@@ -38210,7 +38168,7 @@
         </is>
       </c>
       <c r="O398" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -38242,10 +38200,10 @@
         </is>
       </c>
       <c r="Y398" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="Z398" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="AA398" t="n">
         <v>1</v>
@@ -38254,10 +38212,10 @@
         <v>1</v>
       </c>
       <c r="AC398" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD398" t="n">
-        <v>0.8929999999999999</v>
+        <v>0.4585</v>
       </c>
     </row>
     <row r="399">
@@ -38306,7 +38264,7 @@
         </is>
       </c>
       <c r="O399" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="P399" t="inlineStr">
         <is>
@@ -38338,10 +38296,10 @@
         </is>
       </c>
       <c r="Y399" t="n">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="Z399" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="AA399" t="n">
         <v>0.74</v>
@@ -38350,10 +38308,10 @@
         <v>0.62</v>
       </c>
       <c r="AC399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD399" t="n">
-        <v>0.847</v>
+        <v>0.5774999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -38402,7 +38360,7 @@
         </is>
       </c>
       <c r="O400" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -38434,10 +38392,10 @@
         </is>
       </c>
       <c r="Y400" t="n">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="Z400" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="AA400" t="n">
         <v>0.47</v>
@@ -38446,10 +38404,10 @@
         <v>0.48</v>
       </c>
       <c r="AC400" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD400" t="n">
-        <v>0.7754999999999999</v>
+        <v>0.5199999999999999</v>
       </c>
     </row>
     <row r="401">
@@ -38498,7 +38456,7 @@
         </is>
       </c>
       <c r="O401" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -38530,7 +38488,7 @@
         </is>
       </c>
       <c r="Y401" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="Z401" t="n">
         <v>0</v>
@@ -38545,7 +38503,7 @@
         <v>1</v>
       </c>
       <c r="AD401" t="n">
-        <v>0.545</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="402">
@@ -38594,7 +38552,7 @@
         </is>
       </c>
       <c r="O402" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
@@ -38626,10 +38584,10 @@
         </is>
       </c>
       <c r="Y402" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="Z402" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA402" t="n">
         <v>0.62</v>
@@ -38641,7 +38599,7 @@
         <v>2</v>
       </c>
       <c r="AD402" t="n">
-        <v>0.4365</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="403">
@@ -38690,7 +38648,7 @@
         </is>
       </c>
       <c r="O403" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -38722,7 +38680,7 @@
         </is>
       </c>
       <c r="Y403" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="Z403" t="n">
         <v>0</v>
@@ -38737,7 +38695,7 @@
         <v>3</v>
       </c>
       <c r="AD403" t="n">
-        <v>0.3635</v>
+        <v>0.3455</v>
       </c>
     </row>
     <row r="404">
@@ -38786,7 +38744,7 @@
         </is>
       </c>
       <c r="O404" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
@@ -38818,10 +38776,10 @@
         </is>
       </c>
       <c r="Y404" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Z404" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AA404" t="n">
         <v>1</v>
@@ -38833,7 +38791,7 @@
         <v>1</v>
       </c>
       <c r="AD404" t="n">
-        <v>0.804</v>
+        <v>0.7905000000000001</v>
       </c>
     </row>
     <row r="405">
@@ -38882,7 +38840,7 @@
         </is>
       </c>
       <c r="O405" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -38914,10 +38872,10 @@
         </is>
       </c>
       <c r="Y405" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="Z405" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AA405" t="n">
         <v>0.82</v>
@@ -38929,7 +38887,7 @@
         <v>2</v>
       </c>
       <c r="AD405" t="n">
-        <v>0.66</v>
+        <v>0.6435</v>
       </c>
     </row>
     <row r="406">
@@ -38978,7 +38936,7 @@
         </is>
       </c>
       <c r="O406" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -39010,10 +38968,10 @@
         </is>
       </c>
       <c r="Y406" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Z406" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AA406" t="n">
         <v>0.55</v>
@@ -39025,7 +38983,7 @@
         <v>3</v>
       </c>
       <c r="AD406" t="n">
-        <v>0.6045</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="407">
@@ -39077,7 +39035,7 @@
         <v>1.5</v>
       </c>
       <c r="R407" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S407" t="n">
         <v>120</v>
@@ -39171,7 +39129,7 @@
         <v>1.5</v>
       </c>
       <c r="R408" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S408" t="n">
         <v>120</v>
@@ -39265,7 +39223,7 @@
         <v>1.5</v>
       </c>
       <c r="R409" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S409" t="n">
         <v>120</v>
@@ -41048,7 +41006,7 @@
       <c r="O428" t="inlineStr"/>
       <c r="P428" t="inlineStr"/>
       <c r="Q428" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R428" t="n">
         <v>50</v>
@@ -41078,7 +41036,7 @@
         </is>
       </c>
       <c r="Y428" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="Z428" t="n">
         <v>1</v>
@@ -41090,10 +41048,10 @@
         <v>0.22</v>
       </c>
       <c r="AC428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD428" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.7729999999999999</v>
       </c>
     </row>
     <row r="429">
@@ -41142,7 +41100,7 @@
       <c r="O429" t="inlineStr"/>
       <c r="P429" t="inlineStr"/>
       <c r="Q429" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R429" t="n">
         <v>50</v>
@@ -41172,22 +41130,22 @@
         </is>
       </c>
       <c r="Y429" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="Z429" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AA429" t="n">
         <v>0.74</v>
       </c>
       <c r="AB429" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AC429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD429" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="430">
@@ -41236,7 +41194,7 @@
       <c r="O430" t="inlineStr"/>
       <c r="P430" t="inlineStr"/>
       <c r="Q430" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R430" t="n">
         <v>50</v>
@@ -41266,10 +41224,10 @@
         </is>
       </c>
       <c r="Y430" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Z430" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA430" t="n">
         <v>0.89</v>
@@ -41281,7 +41239,7 @@
         <v>3</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.7585</v>
+        <v>0.6775</v>
       </c>
     </row>
     <row r="431">
@@ -41612,7 +41570,7 @@
       <c r="O434" t="inlineStr"/>
       <c r="P434" t="inlineStr"/>
       <c r="Q434" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R434" t="n">
         <v>50</v>
@@ -41642,10 +41600,10 @@
         </is>
       </c>
       <c r="Y434" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="Z434" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="AA434" t="n">
         <v>0.86</v>
@@ -41657,7 +41615,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.4075</v>
+        <v>0.3365</v>
       </c>
     </row>
     <row r="435">
@@ -41706,7 +41664,7 @@
       <c r="O435" t="inlineStr"/>
       <c r="P435" t="inlineStr"/>
       <c r="Q435" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R435" t="n">
         <v>50</v>
@@ -41800,7 +41758,7 @@
       <c r="O436" t="inlineStr"/>
       <c r="P436" t="inlineStr"/>
       <c r="Q436" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R436" t="n">
         <v>50</v>
@@ -41894,10 +41852,10 @@
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
       <c r="Q437" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R437" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S437" t="n">
         <v>120</v>
@@ -41924,10 +41882,10 @@
         </is>
       </c>
       <c r="Y437" t="n">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
       <c r="Z437" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="AA437" t="n">
         <v>0.88</v>
@@ -41939,7 +41897,7 @@
         <v>1</v>
       </c>
       <c r="AD437" t="n">
-        <v>0.3305</v>
+        <v>0.4815</v>
       </c>
     </row>
     <row r="438">
@@ -41988,10 +41946,10 @@
       <c r="O438" t="inlineStr"/>
       <c r="P438" t="inlineStr"/>
       <c r="Q438" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R438" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S438" t="n">
         <v>120</v>
@@ -42018,7 +41976,7 @@
         </is>
       </c>
       <c r="Y438" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z438" t="n">
         <v>0</v>
@@ -42033,7 +41991,7 @@
         <v>2</v>
       </c>
       <c r="AD438" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="439">
@@ -42082,10 +42040,10 @@
       <c r="O439" t="inlineStr"/>
       <c r="P439" t="inlineStr"/>
       <c r="Q439" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R439" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S439" t="n">
         <v>120</v>
@@ -43304,7 +43262,7 @@
       <c r="O452" t="inlineStr"/>
       <c r="P452" t="inlineStr"/>
       <c r="Q452" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R452" t="n">
         <v>80</v>
@@ -43398,7 +43356,7 @@
       <c r="O453" t="inlineStr"/>
       <c r="P453" t="inlineStr"/>
       <c r="Q453" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R453" t="n">
         <v>80</v>
@@ -43492,7 +43450,7 @@
       <c r="O454" t="inlineStr"/>
       <c r="P454" t="inlineStr"/>
       <c r="Q454" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R454" t="n">
         <v>80</v>
@@ -43868,7 +43826,7 @@
       <c r="O458" t="inlineStr"/>
       <c r="P458" t="inlineStr"/>
       <c r="Q458" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R458" t="n">
         <v>50</v>
@@ -43898,10 +43856,10 @@
         </is>
       </c>
       <c r="Y458" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="Z458" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AA458" t="n">
         <v>0.88</v>
@@ -43913,7 +43871,7 @@
         <v>1</v>
       </c>
       <c r="AD458" t="n">
-        <v>0.406</v>
+        <v>0.3305</v>
       </c>
     </row>
     <row r="459">
@@ -43962,7 +43920,7 @@
       <c r="O459" t="inlineStr"/>
       <c r="P459" t="inlineStr"/>
       <c r="Q459" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R459" t="n">
         <v>50</v>
@@ -43992,7 +43950,7 @@
         </is>
       </c>
       <c r="Y459" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Z459" t="n">
         <v>0</v>
@@ -44007,7 +43965,7 @@
         <v>2</v>
       </c>
       <c r="AD459" t="n">
-        <v>0.2145</v>
+        <v>0.2115</v>
       </c>
     </row>
     <row r="460">
@@ -44056,7 +44014,7 @@
       <c r="O460" t="inlineStr"/>
       <c r="P460" t="inlineStr"/>
       <c r="Q460" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R460" t="n">
         <v>50</v>
@@ -44153,7 +44111,7 @@
         <v>1.5</v>
       </c>
       <c r="R461" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S461" t="n">
         <v>120</v>
@@ -44247,7 +44205,7 @@
         <v>1.5</v>
       </c>
       <c r="R462" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S462" t="n">
         <v>120</v>
@@ -44341,7 +44299,7 @@
         <v>1.5</v>
       </c>
       <c r="R463" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S463" t="n">
         <v>120</v>
@@ -44717,7 +44675,7 @@
         <v>2.75</v>
       </c>
       <c r="R467" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S467" t="n">
         <v>120</v>
@@ -44811,7 +44769,7 @@
         <v>2.75</v>
       </c>
       <c r="R468" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S468" t="n">
         <v>120</v>
@@ -44905,7 +44863,7 @@
         <v>2.75</v>
       </c>
       <c r="R469" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S469" t="n">
         <v>120</v>
@@ -44996,7 +44954,7 @@
       <c r="O470" t="inlineStr"/>
       <c r="P470" t="inlineStr"/>
       <c r="Q470" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R470" t="n">
         <v>35</v>
@@ -45026,10 +44984,10 @@
         </is>
       </c>
       <c r="Y470" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="Z470" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="AA470" t="n">
         <v>0.74</v>
@@ -45041,7 +44999,7 @@
         <v>2</v>
       </c>
       <c r="AD470" t="n">
-        <v>0.7975</v>
+        <v>0.8335</v>
       </c>
     </row>
     <row r="471">
@@ -45090,7 +45048,7 @@
       <c r="O471" t="inlineStr"/>
       <c r="P471" t="inlineStr"/>
       <c r="Q471" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R471" t="n">
         <v>35</v>
@@ -45120,10 +45078,10 @@
         </is>
       </c>
       <c r="Y471" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="Z471" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="AA471" t="n">
         <v>1</v>
@@ -45135,7 +45093,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.8815000000000001</v>
       </c>
     </row>
     <row r="472">
@@ -45184,7 +45142,7 @@
       <c r="O472" t="inlineStr"/>
       <c r="P472" t="inlineStr"/>
       <c r="Q472" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R472" t="n">
         <v>35</v>
@@ -45214,22 +45172,22 @@
         </is>
       </c>
       <c r="Y472" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="Z472" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA472" t="n">
         <v>0.92</v>
       </c>
       <c r="AB472" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="AC472" t="n">
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.7989999999999999</v>
       </c>
     </row>
     <row r="473">
@@ -47534,7 +47492,7 @@
       <c r="O497" t="inlineStr"/>
       <c r="P497" t="inlineStr"/>
       <c r="Q497" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R497" t="n">
         <v>35</v>
@@ -47564,10 +47522,10 @@
         </is>
       </c>
       <c r="Y497" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="Z497" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="AA497" t="n">
         <v>0.68</v>
@@ -47579,7 +47537,7 @@
         <v>2</v>
       </c>
       <c r="AD497" t="n">
-        <v>0.7675</v>
+        <v>0.8095</v>
       </c>
     </row>
     <row r="498">
@@ -47628,7 +47586,7 @@
       <c r="O498" t="inlineStr"/>
       <c r="P498" t="inlineStr"/>
       <c r="Q498" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R498" t="n">
         <v>35</v>
@@ -47658,10 +47616,10 @@
         </is>
       </c>
       <c r="Y498" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="Z498" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="AA498" t="n">
         <v>0.9</v>
@@ -47673,7 +47631,7 @@
         <v>1</v>
       </c>
       <c r="AD498" t="n">
-        <v>0.772</v>
+        <v>0.8405</v>
       </c>
     </row>
     <row r="499">
@@ -47722,7 +47680,7 @@
       <c r="O499" t="inlineStr"/>
       <c r="P499" t="inlineStr"/>
       <c r="Q499" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R499" t="n">
         <v>35</v>
@@ -47752,22 +47710,22 @@
         </is>
       </c>
       <c r="Y499" t="n">
-        <v>0.53</v>
+        <v>0.68</v>
       </c>
       <c r="Z499" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA499" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AB499" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="AC499" t="n">
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.6365000000000001</v>
+        <v>0.7729999999999999</v>
       </c>
     </row>
     <row r="500">
@@ -49793,7 +49751,7 @@
         <v>1.5</v>
       </c>
       <c r="R521" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S521" t="n">
         <v>120</v>
@@ -49829,13 +49787,13 @@
         <v>0.9</v>
       </c>
       <c r="AB521" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="AC521" t="n">
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.8435</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="522">
@@ -49887,7 +49845,7 @@
         <v>1.5</v>
       </c>
       <c r="R522" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S522" t="n">
         <v>120</v>
@@ -49981,7 +49939,7 @@
         <v>1.5</v>
       </c>
       <c r="R523" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S523" t="n">
         <v>120</v>
@@ -50639,7 +50597,7 @@
         <v>1.5</v>
       </c>
       <c r="R530" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S530" t="n">
         <v>120</v>
@@ -50733,7 +50691,7 @@
         <v>1.5</v>
       </c>
       <c r="R531" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S531" t="n">
         <v>120</v>
@@ -50827,7 +50785,7 @@
         <v>1.5</v>
       </c>
       <c r="R532" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S532" t="n">
         <v>120</v>
@@ -52046,7 +52004,7 @@
       <c r="O545" t="inlineStr"/>
       <c r="P545" t="inlineStr"/>
       <c r="Q545" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R545" t="n">
         <v>50</v>
@@ -52088,7 +52046,7 @@
         <v>0.15</v>
       </c>
       <c r="AC545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD545" t="n">
         <v>0.6764999999999999</v>
@@ -52140,7 +52098,7 @@
       <c r="O546" t="inlineStr"/>
       <c r="P546" t="inlineStr"/>
       <c r="Q546" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R546" t="n">
         <v>50</v>
@@ -52170,10 +52128,10 @@
         </is>
       </c>
       <c r="Y546" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="Z546" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AA546" t="n">
         <v>0.77</v>
@@ -52185,7 +52143,7 @@
         <v>1</v>
       </c>
       <c r="AD546" t="n">
-        <v>0.7785</v>
+        <v>0.8270000000000001</v>
       </c>
     </row>
     <row r="547">
@@ -52234,7 +52192,7 @@
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="inlineStr"/>
       <c r="Q547" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R547" t="n">
         <v>50</v>
@@ -52264,10 +52222,10 @@
         </is>
       </c>
       <c r="Y547" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z547" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA547" t="n">
         <v>0.9399999999999999</v>
@@ -52276,10 +52234,10 @@
         <v>0.67</v>
       </c>
       <c r="AC547" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD547" t="n">
-        <v>0.6395</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="548">
@@ -52610,7 +52568,7 @@
       <c r="O551" t="inlineStr"/>
       <c r="P551" t="inlineStr"/>
       <c r="Q551" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R551" t="n">
         <v>50</v>
@@ -52640,10 +52598,10 @@
         </is>
       </c>
       <c r="Y551" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="Z551" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="AA551" t="n">
         <v>0.68</v>
@@ -52652,10 +52610,10 @@
         <v>0.35</v>
       </c>
       <c r="AC551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD551" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.7675</v>
       </c>
     </row>
     <row r="552">
@@ -52704,7 +52662,7 @@
       <c r="O552" t="inlineStr"/>
       <c r="P552" t="inlineStr"/>
       <c r="Q552" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R552" t="n">
         <v>50</v>
@@ -52734,10 +52692,10 @@
         </is>
       </c>
       <c r="Y552" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="Z552" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AA552" t="n">
         <v>0.89</v>
@@ -52746,10 +52704,10 @@
         <v>0.76</v>
       </c>
       <c r="AC552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD552" t="n">
-        <v>0.8385</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="553">
@@ -52798,7 +52756,7 @@
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="inlineStr"/>
       <c r="Q553" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R553" t="n">
         <v>50</v>
@@ -52828,10 +52786,10 @@
         </is>
       </c>
       <c r="Y553" t="n">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
       <c r="Z553" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="AA553" t="n">
         <v>0.9399999999999999</v>
@@ -52843,7 +52801,7 @@
         <v>3</v>
       </c>
       <c r="AD553" t="n">
-        <v>0.7310000000000001</v>
+        <v>0.6335</v>
       </c>
     </row>
     <row r="554">
@@ -53738,7 +53696,7 @@
       <c r="O563" t="inlineStr"/>
       <c r="P563" t="inlineStr"/>
       <c r="Q563" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R563" t="n">
         <v>35</v>
@@ -53768,10 +53726,10 @@
         </is>
       </c>
       <c r="Y563" t="n">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="Z563" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="AA563" t="n">
         <v>0.67</v>
@@ -53780,10 +53738,10 @@
         <v>0.35</v>
       </c>
       <c r="AC563" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD563" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.7955</v>
       </c>
     </row>
     <row r="564">
@@ -53832,7 +53790,7 @@
       <c r="O564" t="inlineStr"/>
       <c r="P564" t="inlineStr"/>
       <c r="Q564" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R564" t="n">
         <v>35</v>
@@ -53862,10 +53820,10 @@
         </is>
       </c>
       <c r="Y564" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="Z564" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="AA564" t="n">
         <v>0.87</v>
@@ -53874,10 +53832,10 @@
         <v>0.76</v>
       </c>
       <c r="AC564" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD564" t="n">
-        <v>0.745</v>
+        <v>0.8195</v>
       </c>
     </row>
     <row r="565">
@@ -53926,7 +53884,7 @@
       <c r="O565" t="inlineStr"/>
       <c r="P565" t="inlineStr"/>
       <c r="Q565" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R565" t="n">
         <v>35</v>
@@ -53956,10 +53914,10 @@
         </is>
       </c>
       <c r="Y565" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="Z565" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA565" t="n">
         <v>0.95</v>
@@ -53971,7 +53929,7 @@
         <v>3</v>
       </c>
       <c r="AD565" t="n">
-        <v>0.6025</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="566">
@@ -54869,7 +54827,7 @@
         <v>1.5</v>
       </c>
       <c r="R575" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S575" t="n">
         <v>120</v>
@@ -54963,7 +54921,7 @@
         <v>1.5</v>
       </c>
       <c r="R576" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S576" t="n">
         <v>120</v>
@@ -55057,7 +55015,7 @@
         <v>1.5</v>
       </c>
       <c r="R577" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S577" t="n">
         <v>120</v>

--- a/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_01.xlsx
+++ b/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_01.xlsx
@@ -38069,7 +38069,7 @@
         <v>3</v>
       </c>
       <c r="AD407" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="408">
@@ -38342,7 +38342,7 @@
         <v>0.9</v>
       </c>
       <c r="AA410" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="AB410" t="n">
         <v>0.29</v>
@@ -38351,7 +38351,7 @@
         <v>2</v>
       </c>
       <c r="AD410" t="n">
-        <v>0.7484999999999999</v>
+        <v>0.7665</v>
       </c>
     </row>
     <row r="411">
@@ -38436,7 +38436,7 @@
         <v>0.71</v>
       </c>
       <c r="AA411" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB411" t="n">
         <v>0.64</v>
@@ -38445,7 +38445,7 @@
         <v>1</v>
       </c>
       <c r="AD411" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.7675</v>
       </c>
     </row>
     <row r="412">
@@ -38530,7 +38530,7 @@
         <v>0.51</v>
       </c>
       <c r="AA412" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="AB412" t="n">
         <v>0.85</v>
@@ -38539,7 +38539,7 @@
         <v>3</v>
       </c>
       <c r="AD412" t="n">
-        <v>0.6759999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="413">
@@ -38821,7 +38821,7 @@
         <v>3</v>
       </c>
       <c r="AD415" t="n">
-        <v>0.5315000000000001</v>
+        <v>0.5315</v>
       </c>
     </row>
     <row r="416">
@@ -39009,7 +39009,7 @@
         <v>1</v>
       </c>
       <c r="AD417" t="n">
-        <v>0.8049999999999999</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="418">
@@ -39479,7 +39479,7 @@
         <v>1</v>
       </c>
       <c r="AD422" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="423">
@@ -39564,7 +39564,7 @@
         <v>0.58</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB423" t="n">
         <v>0.52</v>
@@ -39573,7 +39573,7 @@
         <v>2</v>
       </c>
       <c r="AD423" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="424">
@@ -39658,7 +39658,7 @@
         <v>0.38</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB424" t="n">
         <v>0.67</v>
@@ -39667,7 +39667,7 @@
         <v>3</v>
       </c>
       <c r="AD424" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="425">
@@ -39855,7 +39855,7 @@
         <v>1</v>
       </c>
       <c r="AD426" t="n">
-        <v>0.8119999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="427">
@@ -39949,7 +39949,7 @@
         <v>2</v>
       </c>
       <c r="AD427" t="n">
-        <v>0.7999999999999998</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="428">
@@ -40043,7 +40043,7 @@
         <v>2</v>
       </c>
       <c r="AD428" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="429">
@@ -40137,7 +40137,7 @@
         <v>1</v>
       </c>
       <c r="AD429" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="430">
@@ -40222,7 +40222,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB430" t="n">
         <v>0.52</v>
@@ -40231,7 +40231,7 @@
         <v>3</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.7585</v>
+        <v>0.7665</v>
       </c>
     </row>
     <row r="431">
@@ -40419,7 +40419,7 @@
         <v>2</v>
       </c>
       <c r="AD432" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="433">
@@ -40598,7 +40598,7 @@
         <v>0.64</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB434" t="n">
         <v>0.46</v>
@@ -40607,7 +40607,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="435">
@@ -40692,7 +40692,7 @@
         <v>0.38</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB435" t="n">
         <v>0.67</v>
@@ -40701,7 +40701,7 @@
         <v>2</v>
       </c>
       <c r="AD435" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="436">
@@ -40786,7 +40786,7 @@
         <v>0.13</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AB436" t="n">
         <v>0.48</v>
@@ -40795,7 +40795,7 @@
         <v>3</v>
       </c>
       <c r="AD436" t="n">
-        <v>0.2075</v>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="437">
@@ -41171,7 +41171,7 @@
         <v>1</v>
       </c>
       <c r="AD440" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="441">
@@ -41256,7 +41256,7 @@
         <v>0.51</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB441" t="n">
         <v>0.57</v>
@@ -41265,7 +41265,7 @@
         <v>2</v>
       </c>
       <c r="AD441" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="442">
@@ -41350,7 +41350,7 @@
         <v>0.19</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB442" t="n">
         <v>0.52</v>
@@ -41359,7 +41359,7 @@
         <v>3</v>
       </c>
       <c r="AD442" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="443">
@@ -41547,7 +41547,7 @@
         <v>2</v>
       </c>
       <c r="AD444" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -41735,7 +41735,7 @@
         <v>1</v>
       </c>
       <c r="AD446" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="447">
@@ -41820,7 +41820,7 @@
         <v>0.51</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB447" t="n">
         <v>0.57</v>
@@ -41829,7 +41829,7 @@
         <v>2</v>
       </c>
       <c r="AD447" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="448">
@@ -41914,7 +41914,7 @@
         <v>0.19</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB448" t="n">
         <v>0.52</v>
@@ -41923,7 +41923,7 @@
         <v>3</v>
       </c>
       <c r="AD448" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="449">
@@ -42290,7 +42290,7 @@
         <v>0.08</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB452" t="n">
         <v>0.67</v>
@@ -42299,7 +42299,7 @@
         <v>1</v>
       </c>
       <c r="AD452" t="n">
-        <v>0.2885</v>
+        <v>0.3065</v>
       </c>
     </row>
     <row r="453">
@@ -42384,7 +42384,7 @@
         <v>0</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB453" t="n">
         <v>0.52</v>
@@ -42393,7 +42393,7 @@
         <v>2</v>
       </c>
       <c r="AD453" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="454">
@@ -42478,7 +42478,7 @@
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AB454" t="n">
         <v>0.4</v>
@@ -42487,7 +42487,7 @@
         <v>3</v>
       </c>
       <c r="AD454" t="n">
-        <v>0.102</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="455">
@@ -42675,7 +42675,7 @@
         <v>1</v>
       </c>
       <c r="AD456" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="457">
@@ -42769,7 +42769,7 @@
         <v>3</v>
       </c>
       <c r="AD457" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="458">
@@ -43145,7 +43145,7 @@
         <v>3</v>
       </c>
       <c r="AD461" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="462">
@@ -43239,7 +43239,7 @@
         <v>2</v>
       </c>
       <c r="AD462" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="463">
@@ -43615,7 +43615,7 @@
         <v>3</v>
       </c>
       <c r="AD466" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="467">
@@ -43700,7 +43700,7 @@
         <v>0.64</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB467" t="n">
         <v>0.46</v>
@@ -43709,7 +43709,7 @@
         <v>1</v>
       </c>
       <c r="AD467" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="468">
@@ -43794,7 +43794,7 @@
         <v>0.38</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB468" t="n">
         <v>0.67</v>
@@ -43803,7 +43803,7 @@
         <v>2</v>
       </c>
       <c r="AD468" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="469">
@@ -43888,7 +43888,7 @@
         <v>0.19</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB469" t="n">
         <v>0.52</v>
@@ -43897,7 +43897,7 @@
         <v>3</v>
       </c>
       <c r="AD469" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="470">
@@ -44085,7 +44085,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="472">
@@ -44179,7 +44179,7 @@
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="473">
@@ -44367,7 +44367,7 @@
         <v>2</v>
       </c>
       <c r="AD474" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="475">
@@ -44555,7 +44555,7 @@
         <v>1</v>
       </c>
       <c r="AD476" t="n">
-        <v>0.6044999999999999</v>
+        <v>0.6045</v>
       </c>
     </row>
     <row r="477">
@@ -44931,7 +44931,7 @@
         <v>2</v>
       </c>
       <c r="AD480" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="481">
@@ -45016,7 +45016,7 @@
         <v>0.51</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB481" t="n">
         <v>0.57</v>
@@ -45025,7 +45025,7 @@
         <v>3</v>
       </c>
       <c r="AD481" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="482">
@@ -45119,7 +45119,7 @@
         <v>2</v>
       </c>
       <c r="AD482" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="483">
@@ -45298,7 +45298,7 @@
         <v>0.58</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="AB484" t="n">
         <v>0.52</v>
@@ -45307,7 +45307,7 @@
         <v>3</v>
       </c>
       <c r="AD484" t="n">
-        <v>0.571</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="485">
@@ -45401,7 +45401,7 @@
         <v>1</v>
       </c>
       <c r="AD485" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -45683,7 +45683,7 @@
         <v>1</v>
       </c>
       <c r="AD488" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="489">
@@ -45768,7 +45768,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB489" t="n">
         <v>0.67</v>
@@ -45777,7 +45777,7 @@
         <v>2</v>
       </c>
       <c r="AD489" t="n">
-        <v>0.7010000000000001</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="490">
@@ -45862,7 +45862,7 @@
         <v>0.38</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AB490" t="n">
         <v>0.32</v>
@@ -45871,7 +45871,7 @@
         <v>3</v>
       </c>
       <c r="AD490" t="n">
-        <v>0.289</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="491">
@@ -45965,7 +45965,7 @@
         <v>1</v>
       </c>
       <c r="AD491" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="492">
@@ -46153,7 +46153,7 @@
         <v>3</v>
       </c>
       <c r="AD493" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
     </row>
     <row r="494">
@@ -46341,7 +46341,7 @@
         <v>2</v>
       </c>
       <c r="AD495" t="n">
-        <v>0.8379999999999999</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="496">
@@ -46717,7 +46717,7 @@
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="500">
@@ -47093,7 +47093,7 @@
         <v>2</v>
       </c>
       <c r="AD503" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="504">
@@ -47742,7 +47742,7 @@
         <v>0.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AB510" t="n">
         <v>0.46</v>
@@ -47751,7 +47751,7 @@
         <v>2</v>
       </c>
       <c r="AD510" t="n">
-        <v>0.6519999999999999</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="511">
@@ -47836,7 +47836,7 @@
         <v>0.38</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB511" t="n">
         <v>0.67</v>
@@ -47845,7 +47845,7 @@
         <v>3</v>
       </c>
       <c r="AD511" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="512">
@@ -47930,7 +47930,7 @@
         <v>0.64</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB512" t="n">
         <v>0.46</v>
@@ -47939,7 +47939,7 @@
         <v>1</v>
       </c>
       <c r="AD512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="513">
@@ -48024,7 +48024,7 @@
         <v>0.51</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB513" t="n">
         <v>0.57</v>
@@ -48033,7 +48033,7 @@
         <v>2</v>
       </c>
       <c r="AD513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="514">
@@ -48118,7 +48118,7 @@
         <v>0.38</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB514" t="n">
         <v>0.67</v>
@@ -48127,7 +48127,7 @@
         <v>3</v>
       </c>
       <c r="AD514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="515">
@@ -48306,7 +48306,7 @@
         <v>0.51</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB516" t="n">
         <v>0.57</v>
@@ -48315,7 +48315,7 @@
         <v>2</v>
       </c>
       <c r="AD516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="517">
@@ -48400,7 +48400,7 @@
         <v>0.38</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB517" t="n">
         <v>0.67</v>
@@ -48409,7 +48409,7 @@
         <v>3</v>
       </c>
       <c r="AD517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="518">
@@ -48494,7 +48494,7 @@
         <v>0.64</v>
       </c>
       <c r="AA518" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB518" t="n">
         <v>0.46</v>
@@ -48503,7 +48503,7 @@
         <v>1</v>
       </c>
       <c r="AD518" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="519">
@@ -48588,7 +48588,7 @@
         <v>0.51</v>
       </c>
       <c r="AA519" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AB519" t="n">
         <v>0.57</v>
@@ -48597,7 +48597,7 @@
         <v>2</v>
       </c>
       <c r="AD519" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="520">
@@ -48682,7 +48682,7 @@
         <v>0.38</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AB520" t="n">
         <v>0.67</v>
@@ -48691,7 +48691,7 @@
         <v>3</v>
       </c>
       <c r="AD520" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="521">
@@ -48776,7 +48776,7 @@
         <v>0.85</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB521" t="n">
         <v>0.46</v>
@@ -48785,7 +48785,7 @@
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.7985</v>
+        <v>0.8005</v>
       </c>
     </row>
     <row r="522">
@@ -48870,7 +48870,7 @@
         <v>0.77</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB522" t="n">
         <v>0.57</v>
@@ -48879,7 +48879,7 @@
         <v>2</v>
       </c>
       <c r="AD522" t="n">
-        <v>0.768</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="523">
@@ -48964,7 +48964,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB523" t="n">
         <v>0.67</v>
@@ -48973,7 +48973,7 @@
         <v>3</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.7050000000000001</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="524">
@@ -49152,7 +49152,7 @@
         <v>0.51</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB525" t="n">
         <v>0.57</v>
@@ -49161,7 +49161,7 @@
         <v>2</v>
       </c>
       <c r="AD525" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="526">
@@ -49246,7 +49246,7 @@
         <v>0.38</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB526" t="n">
         <v>0.67</v>
@@ -49255,7 +49255,7 @@
         <v>3</v>
       </c>
       <c r="AD526" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="527">
@@ -49443,7 +49443,7 @@
         <v>2</v>
       </c>
       <c r="AD528" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="529">
@@ -49819,7 +49819,7 @@
         <v>3</v>
       </c>
       <c r="AD532" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="533">
@@ -50007,7 +50007,7 @@
         <v>2</v>
       </c>
       <c r="AD534" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="535">
@@ -50289,7 +50289,7 @@
         <v>2</v>
       </c>
       <c r="AD537" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="538">
@@ -50477,7 +50477,7 @@
         <v>1</v>
       </c>
       <c r="AD539" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="540">
@@ -50665,7 +50665,7 @@
         <v>3</v>
       </c>
       <c r="AD541" t="n">
-        <v>0.6339999999999999</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="542">
@@ -50938,7 +50938,7 @@
         <v>0.51</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB544" t="n">
         <v>0.57</v>
@@ -50947,7 +50947,7 @@
         <v>3</v>
       </c>
       <c r="AD544" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="545">
@@ -51041,7 +51041,7 @@
         <v>3</v>
       </c>
       <c r="AD545" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="546">
@@ -51135,7 +51135,7 @@
         <v>1</v>
       </c>
       <c r="AD546" t="n">
-        <v>0.8270000000000001</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="547">
@@ -51323,7 +51323,7 @@
         <v>1</v>
       </c>
       <c r="AD548" t="n">
-        <v>0.7374999999999999</v>
+        <v>0.7375</v>
       </c>
     </row>
     <row r="549">
@@ -51605,7 +51605,7 @@
         <v>2</v>
       </c>
       <c r="AD551" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="552">
@@ -51793,7 +51793,7 @@
         <v>3</v>
       </c>
       <c r="AD553" t="n">
-        <v>0.7310000000000001</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="554">
@@ -52075,7 +52075,7 @@
         <v>3</v>
       </c>
       <c r="AD556" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="557">
@@ -52169,7 +52169,7 @@
         <v>1</v>
       </c>
       <c r="AD557" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="558">
@@ -52254,7 +52254,7 @@
         <v>0.64</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB558" t="n">
         <v>0.46</v>
@@ -52263,7 +52263,7 @@
         <v>2</v>
       </c>
       <c r="AD558" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="559">
@@ -52348,7 +52348,7 @@
         <v>0.51</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB559" t="n">
         <v>0.57</v>
@@ -52357,7 +52357,7 @@
         <v>3</v>
       </c>
       <c r="AD559" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="560">
@@ -52536,7 +52536,7 @@
         <v>0.51</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB561" t="n">
         <v>0.57</v>
@@ -52545,7 +52545,7 @@
         <v>2</v>
       </c>
       <c r="AD561" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="562">
@@ -52630,7 +52630,7 @@
         <v>0.38</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB562" t="n">
         <v>0.67</v>
@@ -52639,7 +52639,7 @@
         <v>3</v>
       </c>
       <c r="AD562" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="563">
@@ -52921,7 +52921,7 @@
         <v>3</v>
       </c>
       <c r="AD565" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="566">
@@ -53485,7 +53485,7 @@
         <v>3</v>
       </c>
       <c r="AD571" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="572">
@@ -53673,7 +53673,7 @@
         <v>2</v>
       </c>
       <c r="AD573" t="n">
-        <v>0.7825000000000001</v>
+        <v>0.7825</v>
       </c>
     </row>
     <row r="574">
@@ -53861,7 +53861,7 @@
         <v>3</v>
       </c>
       <c r="AD575" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="576">
@@ -53955,7 +53955,7 @@
         <v>2</v>
       </c>
       <c r="AD576" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="577">
@@ -54143,7 +54143,7 @@
         <v>1</v>
       </c>
       <c r="AD578" t="n">
-        <v>0.7284999999999999</v>
+        <v>0.7285</v>
       </c>
     </row>
     <row r="579">
@@ -54237,7 +54237,7 @@
         <v>2</v>
       </c>
       <c r="AD579" t="n">
-        <v>0.7024999999999999</v>
+        <v>0.7025</v>
       </c>
     </row>
     <row r="580">
@@ -54425,7 +54425,7 @@
         <v>3</v>
       </c>
       <c r="AD581" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="582">
@@ -54519,7 +54519,7 @@
         <v>1</v>
       </c>
       <c r="AD582" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="583">
@@ -54613,7 +54613,7 @@
         <v>2</v>
       </c>
       <c r="AD583" t="n">
-        <v>0.8139999999999998</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="584">
@@ -54698,7 +54698,7 @@
         <v>0.96</v>
       </c>
       <c r="AA584" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="AB584" t="n">
         <v>0.22</v>
@@ -54707,7 +54707,7 @@
         <v>1</v>
       </c>
       <c r="AD584" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="585">
@@ -54792,7 +54792,7 @@
         <v>0.83</v>
       </c>
       <c r="AA585" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AB585" t="n">
         <v>0.35</v>
@@ -54801,7 +54801,7 @@
         <v>2</v>
       </c>
       <c r="AD585" t="n">
-        <v>0.696</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="586">
@@ -54886,7 +54886,7 @@
         <v>0.64</v>
       </c>
       <c r="AA586" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB586" t="n">
         <v>0.76</v>
@@ -54895,7 +54895,7 @@
         <v>3</v>
       </c>
       <c r="AD586" t="n">
-        <v>0.67</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
   </sheetData>
